--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130307808</v>
+        <v>130307810</v>
       </c>
       <c r="B19" t="n">
         <v>57823</v>
@@ -2442,7 +2442,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444509</v>
+        <v>444410</v>
       </c>
       <c r="R19" t="n">
-        <v>6811987</v>
+        <v>6812061</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2514,27 +2514,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130307843</v>
+        <v>130307808</v>
       </c>
       <c r="B20" t="n">
-        <v>57019</v>
+        <v>57823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2547,7 +2547,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444721</v>
+        <v>444509</v>
       </c>
       <c r="R20" t="n">
-        <v>6812209</v>
+        <v>6811987</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2593,11 +2593,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2624,27 +2619,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130307810</v>
+        <v>130307843</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>57019</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2657,7 +2652,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2667,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444410</v>
+        <v>444721</v>
       </c>
       <c r="R21" t="n">
-        <v>6812061</v>
+        <v>6812209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,6 +2698,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3440,7 +3440,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130307807</v>
+        <v>130307827</v>
       </c>
       <c r="B29" t="n">
         <v>57823</v>
@@ -3473,7 +3473,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444566</v>
+        <v>444700</v>
       </c>
       <c r="R29" t="n">
-        <v>6812030</v>
+        <v>6812211</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130307874</v>
+        <v>130307804</v>
       </c>
       <c r="B30" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3556,34 +3556,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444695</v>
+        <v>444506</v>
       </c>
       <c r="R30" t="n">
-        <v>6812170</v>
+        <v>6812034</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,7 +3650,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130307862</v>
+        <v>130307874</v>
       </c>
       <c r="B31" t="n">
         <v>79180</v>
@@ -3677,10 +3685,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444502</v>
+        <v>444695</v>
       </c>
       <c r="R31" t="n">
-        <v>6812091</v>
+        <v>6812170</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3739,10 +3747,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130307827</v>
+        <v>130307862</v>
       </c>
       <c r="B32" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3750,42 +3758,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444700</v>
+        <v>444502</v>
       </c>
       <c r="R32" t="n">
-        <v>6812211</v>
+        <v>6812091</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130307804</v>
+        <v>130307807</v>
       </c>
       <c r="B33" t="n">
         <v>57823</v>
@@ -3877,7 +3877,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444506</v>
+        <v>444566</v>
       </c>
       <c r="R33" t="n">
-        <v>6812034</v>
+        <v>6812030</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -7941,48 +7941,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130307787</v>
+        <v>130307868</v>
       </c>
       <c r="B73" t="n">
-        <v>91692</v>
+        <v>79180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444683</v>
+        <v>444623</v>
       </c>
       <c r="R73" t="n">
-        <v>6812180</v>
+        <v>6812168</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8023,7 +8020,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8042,10 +8038,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130307868</v>
+        <v>130307790</v>
       </c>
       <c r="B74" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8053,21 +8049,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8077,10 +8073,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444623</v>
+        <v>444667</v>
       </c>
       <c r="R74" t="n">
-        <v>6812168</v>
+        <v>6812191</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8139,45 +8135,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130307790</v>
+        <v>130307787</v>
       </c>
       <c r="B75" t="n">
-        <v>79799</v>
+        <v>91692</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444667</v>
+        <v>444683</v>
       </c>
       <c r="R75" t="n">
-        <v>6812191</v>
+        <v>6812180</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8218,6 +8217,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130307789</v>
+        <v>130307846</v>
       </c>
       <c r="B14" t="n">
-        <v>79799</v>
+        <v>78938</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,21 +1911,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444433</v>
+        <v>444569</v>
       </c>
       <c r="R14" t="n">
-        <v>6811944</v>
+        <v>6812062</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130307846</v>
+        <v>130307789</v>
       </c>
       <c r="B16" t="n">
-        <v>78938</v>
+        <v>79799</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,21 +2113,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444569</v>
+        <v>444433</v>
       </c>
       <c r="R16" t="n">
-        <v>6812062</v>
+        <v>6811944</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130307810</v>
+        <v>130307808</v>
       </c>
       <c r="B19" t="n">
         <v>57823</v>
@@ -2442,7 +2442,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444410</v>
+        <v>444509</v>
       </c>
       <c r="R19" t="n">
-        <v>6812061</v>
+        <v>6811987</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2514,27 +2514,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130307808</v>
+        <v>130307843</v>
       </c>
       <c r="B20" t="n">
-        <v>57823</v>
+        <v>57019</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2547,7 +2547,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444509</v>
+        <v>444721</v>
       </c>
       <c r="R20" t="n">
-        <v>6811987</v>
+        <v>6812209</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2593,6 +2593,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2619,27 +2624,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130307843</v>
+        <v>130307810</v>
       </c>
       <c r="B21" t="n">
-        <v>57019</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2652,7 +2657,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2662,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444721</v>
+        <v>444410</v>
       </c>
       <c r="R21" t="n">
-        <v>6812209</v>
+        <v>6812061</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2698,11 +2703,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -7112,7 +7112,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130307815</v>
+        <v>130307835</v>
       </c>
       <c r="B65" t="n">
         <v>57823</v>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444464</v>
+        <v>444643</v>
       </c>
       <c r="R65" t="n">
-        <v>6812074</v>
+        <v>6812117</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130307835</v>
+        <v>130307815</v>
       </c>
       <c r="B66" t="n">
         <v>57823</v>
@@ -7260,10 +7260,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444643</v>
+        <v>444464</v>
       </c>
       <c r="R66" t="n">
-        <v>6812117</v>
+        <v>6812074</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7941,45 +7941,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130307868</v>
+        <v>130307787</v>
       </c>
       <c r="B73" t="n">
-        <v>79180</v>
+        <v>91692</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444623</v>
+        <v>444683</v>
       </c>
       <c r="R73" t="n">
-        <v>6812168</v>
+        <v>6812180</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8020,6 +8023,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8038,10 +8042,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130307790</v>
+        <v>130307868</v>
       </c>
       <c r="B74" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8049,21 +8053,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8073,10 +8077,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444667</v>
+        <v>444623</v>
       </c>
       <c r="R74" t="n">
-        <v>6812191</v>
+        <v>6812168</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8135,48 +8139,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130307787</v>
+        <v>130307790</v>
       </c>
       <c r="B75" t="n">
-        <v>91692</v>
+        <v>79799</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444683</v>
+        <v>444667</v>
       </c>
       <c r="R75" t="n">
-        <v>6812180</v>
+        <v>6812191</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8217,7 +8218,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130307814</v>
+        <v>130307867</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,31 +985,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1017,10 +1012,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444450</v>
+        <v>444623</v>
       </c>
       <c r="R5" t="n">
-        <v>6812087</v>
+        <v>6812136</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,6 +1056,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1079,53 +1075,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130307845</v>
+        <v>130307876</v>
       </c>
       <c r="B6" t="n">
-        <v>98954</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444430</v>
+        <v>444651</v>
       </c>
       <c r="R6" t="n">
-        <v>6812024</v>
+        <v>6812124</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,7 +1154,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130307867</v>
+        <v>130307850</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,37 +1183,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444623</v>
+        <v>444442</v>
       </c>
       <c r="R7" t="n">
-        <v>6812136</v>
+        <v>6811950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,7 +1251,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1286,10 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130307876</v>
+        <v>130307825</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,34 +1280,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444651</v>
+        <v>444646</v>
       </c>
       <c r="R8" t="n">
-        <v>6812124</v>
+        <v>6812173</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130307850</v>
+        <v>130307839</v>
       </c>
       <c r="B9" t="n">
-        <v>78937</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,34 +1385,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444442</v>
+        <v>444522</v>
       </c>
       <c r="R9" t="n">
-        <v>6811950</v>
+        <v>6811930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,32 +1479,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130307825</v>
+        <v>130307795</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57016</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1513,7 +1512,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1523,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444646</v>
+        <v>444500</v>
       </c>
       <c r="R10" t="n">
-        <v>6812173</v>
+        <v>6812038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,7 +1584,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130307839</v>
+        <v>130307814</v>
       </c>
       <c r="B11" t="n">
         <v>57823</v>
@@ -1618,7 +1617,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1628,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444522</v>
+        <v>444450</v>
       </c>
       <c r="R11" t="n">
-        <v>6811930</v>
+        <v>6812087</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130307795</v>
+        <v>130307845</v>
       </c>
       <c r="B12" t="n">
-        <v>57016</v>
+        <v>98954</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,31 +1700,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1733,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444500</v>
+        <v>444430</v>
       </c>
       <c r="R12" t="n">
-        <v>6812038</v>
+        <v>6812024</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,6 +1776,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130307846</v>
+        <v>130307789</v>
       </c>
       <c r="B14" t="n">
-        <v>78938</v>
+        <v>79799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,21 +1911,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444569</v>
+        <v>444433</v>
       </c>
       <c r="R14" t="n">
-        <v>6812062</v>
+        <v>6811944</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130307789</v>
+        <v>130307846</v>
       </c>
       <c r="B16" t="n">
-        <v>79799</v>
+        <v>78938</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,21 +2113,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444433</v>
+        <v>444569</v>
       </c>
       <c r="R16" t="n">
-        <v>6811944</v>
+        <v>6812062</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130307809</v>
+        <v>130307877</v>
       </c>
       <c r="B45" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,42 +5083,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444452</v>
+        <v>444661</v>
       </c>
       <c r="R45" t="n">
-        <v>6812004</v>
+        <v>6812100</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5177,10 +5169,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130307831</v>
+        <v>130307851</v>
       </c>
       <c r="B46" t="n">
-        <v>57823</v>
+        <v>78937</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5188,42 +5180,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444733</v>
+        <v>444648</v>
       </c>
       <c r="R46" t="n">
-        <v>6812210</v>
+        <v>6812167</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5282,7 +5266,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130307820</v>
+        <v>130307831</v>
       </c>
       <c r="B47" t="n">
         <v>57823</v>
@@ -5325,10 +5309,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444459</v>
+        <v>444733</v>
       </c>
       <c r="R47" t="n">
-        <v>6812090</v>
+        <v>6812210</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5387,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130307877</v>
+        <v>130307820</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5398,34 +5382,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444661</v>
+        <v>444459</v>
       </c>
       <c r="R48" t="n">
-        <v>6812100</v>
+        <v>6812090</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5484,10 +5476,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130307851</v>
+        <v>130307809</v>
       </c>
       <c r="B49" t="n">
-        <v>78937</v>
+        <v>57823</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5495,34 +5487,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444648</v>
+        <v>444452</v>
       </c>
       <c r="R49" t="n">
-        <v>6812167</v>
+        <v>6812004</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130307875</v>
+        <v>130307806</v>
       </c>
       <c r="B62" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6820,34 +6820,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444676</v>
+        <v>444656</v>
       </c>
       <c r="R62" t="n">
-        <v>6812126</v>
+        <v>6812108</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6906,7 +6914,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130307864</v>
+        <v>130307875</v>
       </c>
       <c r="B63" t="n">
         <v>79180</v>
@@ -6935,19 +6943,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444533</v>
+        <v>444676</v>
       </c>
       <c r="R63" t="n">
-        <v>6812085</v>
+        <v>6812126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6988,7 +6993,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7007,10 +7011,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130307806</v>
+        <v>130307864</v>
       </c>
       <c r="B64" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7018,31 +7022,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7050,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444656</v>
+        <v>444533</v>
       </c>
       <c r="R64" t="n">
-        <v>6812108</v>
+        <v>6812085</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7094,6 +7093,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7629,45 +7629,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130307865</v>
+        <v>130307796</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>57016</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444550</v>
+        <v>444508</v>
       </c>
       <c r="R70" t="n">
-        <v>6812103</v>
+        <v>6811946</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7700,6 +7708,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7726,53 +7739,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130307796</v>
+        <v>130307865</v>
       </c>
       <c r="B71" t="n">
-        <v>57016</v>
+        <v>79180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444508</v>
+        <v>444550</v>
       </c>
       <c r="R71" t="n">
-        <v>6811946</v>
+        <v>6812103</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7805,11 +7810,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130307858</v>
+        <v>130307802</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444436</v>
+        <v>444397</v>
       </c>
       <c r="R2" t="n">
-        <v>6811920</v>
+        <v>6812004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130307860</v>
+        <v>130307858</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444487</v>
+        <v>444436</v>
       </c>
       <c r="R3" t="n">
-        <v>6812030</v>
+        <v>6811920</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130307802</v>
+        <v>130307860</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444397</v>
+        <v>444487</v>
       </c>
       <c r="R4" t="n">
-        <v>6812004</v>
+        <v>6812030</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130307867</v>
+        <v>130307850</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,37 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444623</v>
+        <v>444442</v>
       </c>
       <c r="R5" t="n">
-        <v>6812136</v>
+        <v>6811950</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1053,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1075,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130307876</v>
+        <v>130307867</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,16 +1100,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444651</v>
+        <v>444623</v>
       </c>
       <c r="R6" t="n">
-        <v>6812124</v>
+        <v>6812136</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,6 +1153,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1172,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130307850</v>
+        <v>130307876</v>
       </c>
       <c r="B7" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,21 +1183,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444442</v>
+        <v>444651</v>
       </c>
       <c r="R7" t="n">
-        <v>6811950</v>
+        <v>6812124</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1269,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130307825</v>
+        <v>130307839</v>
       </c>
       <c r="B8" t="n">
         <v>57823</v>
@@ -1302,7 +1302,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444646</v>
+        <v>444522</v>
       </c>
       <c r="R8" t="n">
-        <v>6812173</v>
+        <v>6811930</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130307839</v>
+        <v>130307825</v>
       </c>
       <c r="B9" t="n">
         <v>57823</v>
@@ -1407,7 +1407,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444522</v>
+        <v>444646</v>
       </c>
       <c r="R9" t="n">
-        <v>6811930</v>
+        <v>6812173</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,32 +1479,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130307795</v>
+        <v>130307814</v>
       </c>
       <c r="B10" t="n">
-        <v>57016</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444500</v>
+        <v>444450</v>
       </c>
       <c r="R10" t="n">
-        <v>6812038</v>
+        <v>6812087</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130307814</v>
+        <v>130307795</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1617,7 +1617,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444450</v>
+        <v>444500</v>
       </c>
       <c r="R11" t="n">
-        <v>6812087</v>
+        <v>6812038</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,7 +1692,7 @@
         <v>130307845</v>
       </c>
       <c r="B12" t="n">
-        <v>98954</v>
+        <v>98957</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>130307789</v>
       </c>
       <c r="B14" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>130307846</v>
       </c>
       <c r="B16" t="n">
-        <v>78938</v>
+        <v>78941</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,27 +2304,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130307824</v>
+        <v>130307843</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>57019</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2337,7 +2337,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444617</v>
+        <v>444721</v>
       </c>
       <c r="R18" t="n">
-        <v>6812150</v>
+        <v>6812209</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,6 +2383,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,7 +2414,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130307808</v>
+        <v>130307824</v>
       </c>
       <c r="B19" t="n">
         <v>57823</v>
@@ -2442,7 +2447,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2452,10 +2457,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444509</v>
+        <v>444617</v>
       </c>
       <c r="R19" t="n">
-        <v>6811987</v>
+        <v>6812150</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2514,27 +2519,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130307843</v>
+        <v>130307808</v>
       </c>
       <c r="B20" t="n">
-        <v>57019</v>
+        <v>57823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2547,7 +2552,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2557,10 +2562,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444721</v>
+        <v>444509</v>
       </c>
       <c r="R20" t="n">
-        <v>6812209</v>
+        <v>6811987</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2593,11 +2598,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2729,10 +2729,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130307847</v>
+        <v>130307813</v>
       </c>
       <c r="B22" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,34 +2740,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444648</v>
+        <v>444443</v>
       </c>
       <c r="R22" t="n">
-        <v>6812167</v>
+        <v>6812077</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2834,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130307870</v>
+        <v>130307822</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,34 +2845,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444659</v>
+        <v>444627</v>
       </c>
       <c r="R23" t="n">
-        <v>6812190</v>
+        <v>6812121</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130307869</v>
+        <v>130307819</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2934,34 +2950,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444632</v>
+        <v>444481</v>
       </c>
       <c r="R24" t="n">
-        <v>6812157</v>
+        <v>6812067</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3020,7 +3044,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130307819</v>
+        <v>130307838</v>
       </c>
       <c r="B25" t="n">
         <v>57823</v>
@@ -3063,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444481</v>
+        <v>444516</v>
       </c>
       <c r="R25" t="n">
-        <v>6812067</v>
+        <v>6811940</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,10 +3149,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130307822</v>
+        <v>130307870</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,42 +3160,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444627</v>
+        <v>444659</v>
       </c>
       <c r="R26" t="n">
-        <v>6812121</v>
+        <v>6812190</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3246,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130307838</v>
+        <v>130307869</v>
       </c>
       <c r="B27" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,42 +3257,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444516</v>
+        <v>444632</v>
       </c>
       <c r="R27" t="n">
-        <v>6811940</v>
+        <v>6812157</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3335,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130307813</v>
+        <v>130307847</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>78941</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3346,42 +3354,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444443</v>
+        <v>444648</v>
       </c>
       <c r="R28" t="n">
-        <v>6812077</v>
+        <v>6812167</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130307827</v>
+        <v>130307874</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,42 +3451,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444700</v>
+        <v>444695</v>
       </c>
       <c r="R29" t="n">
-        <v>6812211</v>
+        <v>6812170</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,10 +3537,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130307804</v>
+        <v>130307862</v>
       </c>
       <c r="B30" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3556,42 +3548,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444506</v>
+        <v>444502</v>
       </c>
       <c r="R30" t="n">
-        <v>6812034</v>
+        <v>6812091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3650,10 +3634,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130307874</v>
+        <v>130307827</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3661,34 +3645,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444695</v>
+        <v>444700</v>
       </c>
       <c r="R31" t="n">
-        <v>6812170</v>
+        <v>6812211</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3747,10 +3739,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130307862</v>
+        <v>130307807</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3758,34 +3750,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444502</v>
+        <v>444566</v>
       </c>
       <c r="R32" t="n">
-        <v>6812091</v>
+        <v>6812030</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130307807</v>
+        <v>130307804</v>
       </c>
       <c r="B33" t="n">
         <v>57823</v>
@@ -3877,7 +3877,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444566</v>
+        <v>444506</v>
       </c>
       <c r="R33" t="n">
-        <v>6812030</v>
+        <v>6812034</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130307826</v>
+        <v>130307791</v>
       </c>
       <c r="B35" t="n">
-        <v>57823</v>
+        <v>79802</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4065,42 +4065,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444689</v>
+        <v>444608</v>
       </c>
       <c r="R35" t="n">
-        <v>6812204</v>
+        <v>6812061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4159,10 +4151,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130307791</v>
+        <v>130307826</v>
       </c>
       <c r="B36" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4170,34 +4162,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444608</v>
+        <v>444689</v>
       </c>
       <c r="R36" t="n">
-        <v>6812061</v>
+        <v>6812204</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4571,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130307863</v>
+        <v>130307800</v>
       </c>
       <c r="B40" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4582,34 +4582,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444505</v>
+        <v>444393</v>
       </c>
       <c r="R40" t="n">
-        <v>6812061</v>
+        <v>6812026</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4668,10 +4676,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130307852</v>
+        <v>130307834</v>
       </c>
       <c r="B41" t="n">
-        <v>78937</v>
+        <v>57823</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4679,34 +4687,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444645</v>
+        <v>444688</v>
       </c>
       <c r="R41" t="n">
-        <v>6812074</v>
+        <v>6812170</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4765,10 +4781,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130307871</v>
+        <v>130307852</v>
       </c>
       <c r="B42" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4776,21 +4792,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4800,10 +4816,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444705</v>
+        <v>444645</v>
       </c>
       <c r="R42" t="n">
-        <v>6812214</v>
+        <v>6812074</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4862,10 +4878,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130307800</v>
+        <v>130307863</v>
       </c>
       <c r="B43" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4873,42 +4889,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444393</v>
+        <v>444505</v>
       </c>
       <c r="R43" t="n">
-        <v>6812026</v>
+        <v>6812061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4967,10 +4975,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130307834</v>
+        <v>130307871</v>
       </c>
       <c r="B44" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4978,42 +4986,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444688</v>
+        <v>444705</v>
       </c>
       <c r="R44" t="n">
-        <v>6812170</v>
+        <v>6812214</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130307877</v>
+        <v>130307851</v>
       </c>
       <c r="B45" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,21 +5083,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444661</v>
+        <v>444648</v>
       </c>
       <c r="R45" t="n">
-        <v>6812100</v>
+        <v>6812167</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130307851</v>
+        <v>130307877</v>
       </c>
       <c r="B46" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444648</v>
+        <v>444661</v>
       </c>
       <c r="R46" t="n">
-        <v>6812167</v>
+        <v>6812100</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5266,7 +5266,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130307831</v>
+        <v>130307809</v>
       </c>
       <c r="B47" t="n">
         <v>57823</v>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444733</v>
+        <v>444452</v>
       </c>
       <c r="R47" t="n">
-        <v>6812210</v>
+        <v>6812004</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5476,7 +5476,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130307809</v>
+        <v>130307831</v>
       </c>
       <c r="B49" t="n">
         <v>57823</v>
@@ -5519,10 +5519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444452</v>
+        <v>444733</v>
       </c>
       <c r="R49" t="n">
-        <v>6812004</v>
+        <v>6812210</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5581,10 +5581,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130307836</v>
+        <v>130307866</v>
       </c>
       <c r="B50" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5592,42 +5592,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444552</v>
+        <v>444583</v>
       </c>
       <c r="R50" t="n">
-        <v>6811979</v>
+        <v>6812106</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5686,10 +5678,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130307811</v>
+        <v>130307861</v>
       </c>
       <c r="B51" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5697,42 +5689,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444426</v>
+        <v>444477</v>
       </c>
       <c r="R51" t="n">
-        <v>6812079</v>
+        <v>6812077</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5791,7 +5775,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130307805</v>
+        <v>130307837</v>
       </c>
       <c r="B52" t="n">
         <v>57823</v>
@@ -5834,10 +5818,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444669</v>
+        <v>444516</v>
       </c>
       <c r="R52" t="n">
-        <v>6812147</v>
+        <v>6811948</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,10 +5880,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130307861</v>
+        <v>130307836</v>
       </c>
       <c r="B53" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5907,34 +5891,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444477</v>
+        <v>444552</v>
       </c>
       <c r="R53" t="n">
-        <v>6812077</v>
+        <v>6811979</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5993,10 +5985,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130307866</v>
+        <v>130307818</v>
       </c>
       <c r="B54" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6004,34 +5996,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444583</v>
+        <v>444484</v>
       </c>
       <c r="R54" t="n">
-        <v>6812106</v>
+        <v>6812056</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130307837</v>
+        <v>130307811</v>
       </c>
       <c r="B55" t="n">
         <v>57823</v>
@@ -6123,7 +6123,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444516</v>
+        <v>444426</v>
       </c>
       <c r="R55" t="n">
-        <v>6811948</v>
+        <v>6812079</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6195,7 +6195,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130307818</v>
+        <v>130307805</v>
       </c>
       <c r="B56" t="n">
         <v>57823</v>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444484</v>
+        <v>444669</v>
       </c>
       <c r="R56" t="n">
-        <v>6812056</v>
+        <v>6812147</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130307801</v>
+        <v>130307873</v>
       </c>
       <c r="B58" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6416,42 +6416,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444376</v>
+        <v>444714</v>
       </c>
       <c r="R58" t="n">
-        <v>6812020</v>
+        <v>6812206</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6510,10 +6502,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130307793</v>
+        <v>130307878</v>
       </c>
       <c r="B59" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6521,42 +6513,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444496</v>
+        <v>444642</v>
       </c>
       <c r="R59" t="n">
-        <v>6812068</v>
+        <v>6812075</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6615,10 +6599,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130307873</v>
+        <v>130307801</v>
       </c>
       <c r="B60" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6626,34 +6610,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444714</v>
+        <v>444376</v>
       </c>
       <c r="R60" t="n">
-        <v>6812206</v>
+        <v>6812020</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6712,10 +6704,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130307878</v>
+        <v>130307793</v>
       </c>
       <c r="B61" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6723,34 +6715,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444642</v>
+        <v>444496</v>
       </c>
       <c r="R61" t="n">
-        <v>6812075</v>
+        <v>6812068</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130307806</v>
+        <v>130307875</v>
       </c>
       <c r="B62" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6820,42 +6820,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444656</v>
+        <v>444676</v>
       </c>
       <c r="R62" t="n">
-        <v>6812108</v>
+        <v>6812126</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6914,10 +6906,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130307875</v>
+        <v>130307864</v>
       </c>
       <c r="B63" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6943,16 +6935,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444676</v>
+        <v>444533</v>
       </c>
       <c r="R63" t="n">
-        <v>6812126</v>
+        <v>6812085</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6993,6 +6988,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7011,10 +7007,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130307864</v>
+        <v>130307806</v>
       </c>
       <c r="B64" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7022,26 +7018,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7049,10 +7050,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444533</v>
+        <v>444656</v>
       </c>
       <c r="R64" t="n">
-        <v>6812085</v>
+        <v>6812108</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7093,7 +7094,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7112,7 +7112,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130307835</v>
+        <v>130307833</v>
       </c>
       <c r="B65" t="n">
         <v>57823</v>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444643</v>
+        <v>444702</v>
       </c>
       <c r="R65" t="n">
-        <v>6812117</v>
+        <v>6812194</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130307815</v>
+        <v>130307835</v>
       </c>
       <c r="B66" t="n">
         <v>57823</v>
@@ -7260,10 +7260,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444464</v>
+        <v>444643</v>
       </c>
       <c r="R66" t="n">
-        <v>6812074</v>
+        <v>6812117</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7322,7 +7322,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130307833</v>
+        <v>130307815</v>
       </c>
       <c r="B67" t="n">
         <v>57823</v>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444702</v>
+        <v>444464</v>
       </c>
       <c r="R67" t="n">
-        <v>6812194</v>
+        <v>6812074</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7430,7 +7430,7 @@
         <v>130307859</v>
       </c>
       <c r="B68" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7629,53 +7629,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130307796</v>
+        <v>130307865</v>
       </c>
       <c r="B70" t="n">
-        <v>57016</v>
+        <v>79183</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444508</v>
+        <v>444550</v>
       </c>
       <c r="R70" t="n">
-        <v>6811946</v>
+        <v>6812103</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7708,11 +7700,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7739,45 +7726,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130307865</v>
+        <v>130307796</v>
       </c>
       <c r="B71" t="n">
-        <v>79180</v>
+        <v>57016</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444550</v>
+        <v>444508</v>
       </c>
       <c r="R71" t="n">
-        <v>6812103</v>
+        <v>6811946</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7810,6 +7805,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7944,7 +7944,7 @@
         <v>130307787</v>
       </c>
       <c r="B73" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>130307868</v>
       </c>
       <c r="B74" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>130307790</v>
       </c>
       <c r="B75" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130307802</v>
+        <v>130307858</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444397</v>
+        <v>444436</v>
       </c>
       <c r="R2" t="n">
-        <v>6812004</v>
+        <v>6811920</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130307858</v>
+        <v>130307860</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444436</v>
+        <v>444487</v>
       </c>
       <c r="R3" t="n">
-        <v>6811920</v>
+        <v>6812030</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130307860</v>
+        <v>130307802</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444487</v>
+        <v>444397</v>
       </c>
       <c r="R4" t="n">
-        <v>6812030</v>
+        <v>6812004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130307850</v>
+        <v>130307876</v>
       </c>
       <c r="B5" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444442</v>
+        <v>444651</v>
       </c>
       <c r="R5" t="n">
-        <v>6811950</v>
+        <v>6812124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
         <v>130307867</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130307876</v>
+        <v>130307850</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,21 +1183,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444651</v>
+        <v>444442</v>
       </c>
       <c r="R7" t="n">
-        <v>6812124</v>
+        <v>6811950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,32 +1269,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130307839</v>
+        <v>130307795</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,7 +1302,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444522</v>
+        <v>444500</v>
       </c>
       <c r="R8" t="n">
-        <v>6811930</v>
+        <v>6812038</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130307825</v>
+        <v>130307839</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444646</v>
+        <v>444522</v>
       </c>
       <c r="R9" t="n">
-        <v>6812173</v>
+        <v>6811930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130307814</v>
+        <v>130307825</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444450</v>
+        <v>444646</v>
       </c>
       <c r="R10" t="n">
-        <v>6812087</v>
+        <v>6812173</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130307795</v>
+        <v>130307814</v>
       </c>
       <c r="B11" t="n">
-        <v>57016</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1617,7 +1617,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444500</v>
+        <v>444450</v>
       </c>
       <c r="R11" t="n">
-        <v>6812038</v>
+        <v>6812087</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,7 +1692,7 @@
         <v>130307845</v>
       </c>
       <c r="B12" t="n">
-        <v>98957</v>
+        <v>98983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130307840</v>
       </c>
       <c r="B13" t="n">
-        <v>57667</v>
+        <v>57693</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>130307789</v>
       </c>
       <c r="B14" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>130307829</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>130307846</v>
       </c>
       <c r="B16" t="n">
-        <v>78941</v>
+        <v>78967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>130307817</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,27 +2304,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130307843</v>
+        <v>130307824</v>
       </c>
       <c r="B18" t="n">
-        <v>57019</v>
+        <v>57849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2337,7 +2337,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444721</v>
+        <v>444617</v>
       </c>
       <c r="R18" t="n">
-        <v>6812209</v>
+        <v>6812150</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,11 +2383,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2414,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130307824</v>
+        <v>130307808</v>
       </c>
       <c r="B19" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,7 +2442,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2457,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444617</v>
+        <v>444509</v>
       </c>
       <c r="R19" t="n">
-        <v>6812150</v>
+        <v>6811987</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2519,10 +2514,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130307808</v>
+        <v>130307810</v>
       </c>
       <c r="B20" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2552,7 +2547,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2562,10 +2557,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444509</v>
+        <v>444410</v>
       </c>
       <c r="R20" t="n">
-        <v>6811987</v>
+        <v>6812061</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2624,27 +2619,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130307810</v>
+        <v>130307843</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>57045</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2657,7 +2652,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2667,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444410</v>
+        <v>444721</v>
       </c>
       <c r="R21" t="n">
-        <v>6812061</v>
+        <v>6812209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,6 +2698,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2732,7 +2732,7 @@
         <v>130307813</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>130307822</v>
       </c>
       <c r="B23" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>130307819</v>
       </c>
       <c r="B24" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>130307838</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>130307870</v>
       </c>
       <c r="B26" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>130307869</v>
       </c>
       <c r="B27" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>130307847</v>
       </c>
       <c r="B28" t="n">
-        <v>78941</v>
+        <v>78967</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>130307874</v>
       </c>
       <c r="B29" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>130307862</v>
       </c>
       <c r="B30" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>130307827</v>
       </c>
       <c r="B31" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>130307807</v>
       </c>
       <c r="B32" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>130307804</v>
       </c>
       <c r="B33" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>130307797</v>
       </c>
       <c r="B34" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>130307791</v>
       </c>
       <c r="B35" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>130307826</v>
       </c>
       <c r="B36" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>130307803</v>
       </c>
       <c r="B37" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>130307812</v>
       </c>
       <c r="B38" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>130307828</v>
       </c>
       <c r="B39" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>130307800</v>
       </c>
       <c r="B40" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>130307834</v>
       </c>
       <c r="B41" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130307852</v>
+        <v>130307863</v>
       </c>
       <c r="B42" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4792,21 +4792,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444645</v>
+        <v>444505</v>
       </c>
       <c r="R42" t="n">
-        <v>6812074</v>
+        <v>6812061</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130307863</v>
+        <v>130307852</v>
       </c>
       <c r="B43" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4889,21 +4889,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444505</v>
+        <v>444645</v>
       </c>
       <c r="R43" t="n">
-        <v>6812061</v>
+        <v>6812074</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4978,7 +4978,7 @@
         <v>130307871</v>
       </c>
       <c r="B44" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130307851</v>
+        <v>130307877</v>
       </c>
       <c r="B45" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,21 +5083,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444648</v>
+        <v>444661</v>
       </c>
       <c r="R45" t="n">
-        <v>6812167</v>
+        <v>6812100</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130307877</v>
+        <v>130307851</v>
       </c>
       <c r="B46" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444661</v>
+        <v>444648</v>
       </c>
       <c r="R46" t="n">
-        <v>6812100</v>
+        <v>6812167</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5269,7 +5269,7 @@
         <v>130307809</v>
       </c>
       <c r="B47" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>130307820</v>
       </c>
       <c r="B48" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>130307831</v>
       </c>
       <c r="B49" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5581,10 +5581,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130307866</v>
+        <v>130307861</v>
       </c>
       <c r="B50" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444583</v>
+        <v>444477</v>
       </c>
       <c r="R50" t="n">
-        <v>6812106</v>
+        <v>6812077</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5678,10 +5678,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130307861</v>
+        <v>130307837</v>
       </c>
       <c r="B51" t="n">
-        <v>79183</v>
+        <v>57849</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5689,34 +5689,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444477</v>
+        <v>444516</v>
       </c>
       <c r="R51" t="n">
-        <v>6812077</v>
+        <v>6811948</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5783,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130307837</v>
+        <v>130307836</v>
       </c>
       <c r="B52" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5808,7 +5816,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5818,10 +5826,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444516</v>
+        <v>444552</v>
       </c>
       <c r="R52" t="n">
-        <v>6811948</v>
+        <v>6811979</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5880,10 +5888,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130307836</v>
+        <v>130307818</v>
       </c>
       <c r="B53" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5913,7 +5921,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5923,10 +5931,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444552</v>
+        <v>444484</v>
       </c>
       <c r="R53" t="n">
-        <v>6811979</v>
+        <v>6812056</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5985,10 +5993,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130307818</v>
+        <v>130307811</v>
       </c>
       <c r="B54" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6018,7 +6026,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6028,10 +6036,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444484</v>
+        <v>444426</v>
       </c>
       <c r="R54" t="n">
-        <v>6812056</v>
+        <v>6812079</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,10 +6098,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130307811</v>
+        <v>130307805</v>
       </c>
       <c r="B55" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6123,7 +6131,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6133,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444426</v>
+        <v>444669</v>
       </c>
       <c r="R55" t="n">
-        <v>6812079</v>
+        <v>6812147</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6195,10 +6203,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130307805</v>
+        <v>130307866</v>
       </c>
       <c r="B56" t="n">
-        <v>57823</v>
+        <v>79209</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6206,42 +6214,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444669</v>
+        <v>444583</v>
       </c>
       <c r="R56" t="n">
-        <v>6812147</v>
+        <v>6812106</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6303,7 +6303,7 @@
         <v>130307823</v>
       </c>
       <c r="B57" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130307873</v>
+        <v>130307878</v>
       </c>
       <c r="B58" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444714</v>
+        <v>444642</v>
       </c>
       <c r="R58" t="n">
-        <v>6812206</v>
+        <v>6812075</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6502,10 +6502,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130307878</v>
+        <v>130307801</v>
       </c>
       <c r="B59" t="n">
-        <v>79183</v>
+        <v>57849</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,34 +6513,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444642</v>
+        <v>444376</v>
       </c>
       <c r="R59" t="n">
-        <v>6812075</v>
+        <v>6812020</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6599,10 +6607,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130307801</v>
+        <v>130307873</v>
       </c>
       <c r="B60" t="n">
-        <v>57823</v>
+        <v>79209</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6610,42 +6618,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444376</v>
+        <v>444714</v>
       </c>
       <c r="R60" t="n">
-        <v>6812020</v>
+        <v>6812206</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6707,7 +6707,7 @@
         <v>130307793</v>
       </c>
       <c r="B61" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130307875</v>
+        <v>130307864</v>
       </c>
       <c r="B62" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6838,16 +6838,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444676</v>
+        <v>444533</v>
       </c>
       <c r="R62" t="n">
-        <v>6812126</v>
+        <v>6812085</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6888,6 +6891,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6906,10 +6910,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130307864</v>
+        <v>130307875</v>
       </c>
       <c r="B63" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6935,19 +6939,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444533</v>
+        <v>444676</v>
       </c>
       <c r="R63" t="n">
-        <v>6812085</v>
+        <v>6812126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6988,7 +6989,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>130307806</v>
       </c>
       <c r="B64" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>130307833</v>
       </c>
       <c r="B65" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>130307835</v>
       </c>
       <c r="B66" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>130307815</v>
       </c>
       <c r="B67" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>130307859</v>
       </c>
       <c r="B68" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>130307832</v>
       </c>
       <c r="B69" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>130307865</v>
       </c>
       <c r="B70" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>130307796</v>
       </c>
       <c r="B71" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>130307821</v>
       </c>
       <c r="B72" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7941,48 +7941,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130307787</v>
+        <v>130307790</v>
       </c>
       <c r="B73" t="n">
-        <v>91695</v>
+        <v>79828</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444683</v>
+        <v>444667</v>
       </c>
       <c r="R73" t="n">
-        <v>6812180</v>
+        <v>6812191</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8023,7 +8020,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8045,7 +8041,7 @@
         <v>130307868</v>
       </c>
       <c r="B74" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8139,45 +8135,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130307790</v>
+        <v>130307787</v>
       </c>
       <c r="B75" t="n">
-        <v>79802</v>
+        <v>91721</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444667</v>
+        <v>444683</v>
       </c>
       <c r="R75" t="n">
-        <v>6812191</v>
+        <v>6812180</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8218,6 +8217,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -1071,37 +1071,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130307867</v>
+        <v>130307845</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>98983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1109,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444623</v>
+        <v>444430</v>
       </c>
       <c r="R6" t="n">
-        <v>6812136</v>
+        <v>6812024</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,10 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130307850</v>
+        <v>130307867</v>
       </c>
       <c r="B7" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,34 +1188,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444442</v>
+        <v>444623</v>
       </c>
       <c r="R7" t="n">
-        <v>6811950</v>
+        <v>6812136</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1259,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1269,53 +1278,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130307795</v>
+        <v>130307850</v>
       </c>
       <c r="B8" t="n">
-        <v>57042</v>
+        <v>78966</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444500</v>
+        <v>444442</v>
       </c>
       <c r="R8" t="n">
-        <v>6812038</v>
+        <v>6811950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1689,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130307845</v>
+        <v>130307795</v>
       </c>
       <c r="B12" t="n">
-        <v>98983</v>
+        <v>57042</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,31 +1701,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1732,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444430</v>
+        <v>444500</v>
       </c>
       <c r="R12" t="n">
-        <v>6812024</v>
+        <v>6812038</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,7 +1777,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3634,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130307827</v>
+        <v>130307797</v>
       </c>
       <c r="B31" t="n">
-        <v>57849</v>
+        <v>58011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3645,21 +3645,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3667,7 +3667,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444700</v>
+        <v>444480</v>
       </c>
       <c r="R31" t="n">
-        <v>6812211</v>
+        <v>6812044</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130307807</v>
+        <v>130307827</v>
       </c>
       <c r="B32" t="n">
         <v>57849</v>
@@ -3772,7 +3772,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444566</v>
+        <v>444700</v>
       </c>
       <c r="R32" t="n">
-        <v>6812030</v>
+        <v>6812211</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130307804</v>
+        <v>130307807</v>
       </c>
       <c r="B33" t="n">
         <v>57849</v>
@@ -3877,7 +3877,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444506</v>
+        <v>444566</v>
       </c>
       <c r="R33" t="n">
-        <v>6812034</v>
+        <v>6812030</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130307797</v>
+        <v>130307804</v>
       </c>
       <c r="B34" t="n">
-        <v>58011</v>
+        <v>57849</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3982,7 +3982,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444480</v>
+        <v>444506</v>
       </c>
       <c r="R34" t="n">
-        <v>6812044</v>
+        <v>6812034</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130307861</v>
+        <v>130307866</v>
       </c>
       <c r="B50" t="n">
         <v>79209</v>
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444477</v>
+        <v>444583</v>
       </c>
       <c r="R50" t="n">
-        <v>6812077</v>
+        <v>6812106</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5678,10 +5678,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130307837</v>
+        <v>130307861</v>
       </c>
       <c r="B51" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5689,42 +5689,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444516</v>
+        <v>444477</v>
       </c>
       <c r="R51" t="n">
-        <v>6811948</v>
+        <v>6812077</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5783,7 +5775,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130307836</v>
+        <v>130307837</v>
       </c>
       <c r="B52" t="n">
         <v>57849</v>
@@ -5816,7 +5808,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5826,10 +5818,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444552</v>
+        <v>444516</v>
       </c>
       <c r="R52" t="n">
-        <v>6811979</v>
+        <v>6811948</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5888,7 +5880,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130307818</v>
+        <v>130307836</v>
       </c>
       <c r="B53" t="n">
         <v>57849</v>
@@ -5921,7 +5913,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5931,10 +5923,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444484</v>
+        <v>444552</v>
       </c>
       <c r="R53" t="n">
-        <v>6812056</v>
+        <v>6811979</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5993,7 +5985,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130307811</v>
+        <v>130307818</v>
       </c>
       <c r="B54" t="n">
         <v>57849</v>
@@ -6026,7 +6018,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6036,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444426</v>
+        <v>444484</v>
       </c>
       <c r="R54" t="n">
-        <v>6812079</v>
+        <v>6812056</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6098,7 +6090,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130307805</v>
+        <v>130307811</v>
       </c>
       <c r="B55" t="n">
         <v>57849</v>
@@ -6131,7 +6123,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6141,10 +6133,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444669</v>
+        <v>444426</v>
       </c>
       <c r="R55" t="n">
-        <v>6812147</v>
+        <v>6812079</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6203,10 +6195,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130307866</v>
+        <v>130307805</v>
       </c>
       <c r="B56" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6214,34 +6206,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444583</v>
+        <v>444669</v>
       </c>
       <c r="R56" t="n">
-        <v>6812106</v>
+        <v>6812147</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -974,45 +974,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130307876</v>
+        <v>130307845</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>98984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444651</v>
+        <v>444430</v>
       </c>
       <c r="R5" t="n">
-        <v>6812124</v>
+        <v>6812024</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1071,42 +1080,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130307845</v>
+        <v>130307839</v>
       </c>
       <c r="B6" t="n">
-        <v>98983</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1114,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444430</v>
+        <v>444522</v>
       </c>
       <c r="R6" t="n">
-        <v>6812024</v>
+        <v>6811930</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1167,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1177,37 +1185,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130307867</v>
+        <v>130307795</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>57042</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1215,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444623</v>
+        <v>444500</v>
       </c>
       <c r="R7" t="n">
-        <v>6812136</v>
+        <v>6812038</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1259,7 +1272,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1278,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130307850</v>
+        <v>130307867</v>
       </c>
       <c r="B8" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1289,34 +1301,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444442</v>
+        <v>444623</v>
       </c>
       <c r="R8" t="n">
-        <v>6811950</v>
+        <v>6812136</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,6 +1372,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1375,10 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130307839</v>
+        <v>130307876</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,42 +1402,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444522</v>
+        <v>444651</v>
       </c>
       <c r="R9" t="n">
-        <v>6811930</v>
+        <v>6812124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130307825</v>
+        <v>130307850</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,42 +1499,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444646</v>
+        <v>444442</v>
       </c>
       <c r="R10" t="n">
-        <v>6812173</v>
+        <v>6811950</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130307814</v>
+        <v>130307825</v>
       </c>
       <c r="B11" t="n">
         <v>57849</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444450</v>
+        <v>444646</v>
       </c>
       <c r="R11" t="n">
-        <v>6812087</v>
+        <v>6812173</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,32 +1690,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130307795</v>
+        <v>130307814</v>
       </c>
       <c r="B12" t="n">
-        <v>57042</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444500</v>
+        <v>444450</v>
       </c>
       <c r="R12" t="n">
-        <v>6812038</v>
+        <v>6812087</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2304,7 +2304,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130307824</v>
+        <v>130307808</v>
       </c>
       <c r="B18" t="n">
         <v>57849</v>
@@ -2337,7 +2337,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444617</v>
+        <v>444509</v>
       </c>
       <c r="R18" t="n">
-        <v>6812150</v>
+        <v>6811987</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130307808</v>
+        <v>130307824</v>
       </c>
       <c r="B19" t="n">
         <v>57849</v>
@@ -2442,7 +2442,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444509</v>
+        <v>444617</v>
       </c>
       <c r="R19" t="n">
-        <v>6811987</v>
+        <v>6812150</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130307813</v>
+        <v>130307870</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,42 +2740,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444443</v>
+        <v>444659</v>
       </c>
       <c r="R22" t="n">
-        <v>6812077</v>
+        <v>6812190</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2834,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130307822</v>
+        <v>130307869</v>
       </c>
       <c r="B23" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2845,42 +2837,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444627</v>
+        <v>444632</v>
       </c>
       <c r="R23" t="n">
-        <v>6812121</v>
+        <v>6812157</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,7 +2923,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130307819</v>
+        <v>130307838</v>
       </c>
       <c r="B24" t="n">
         <v>57849</v>
@@ -2982,10 +2966,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444481</v>
+        <v>444516</v>
       </c>
       <c r="R24" t="n">
-        <v>6812067</v>
+        <v>6811940</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3044,10 +3028,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130307838</v>
+        <v>130307847</v>
       </c>
       <c r="B25" t="n">
-        <v>57849</v>
+        <v>78967</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3055,42 +3039,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444516</v>
+        <v>444648</v>
       </c>
       <c r="R25" t="n">
-        <v>6811940</v>
+        <v>6812167</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3149,10 +3125,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130307870</v>
+        <v>130307813</v>
       </c>
       <c r="B26" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3160,34 +3136,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444659</v>
+        <v>444443</v>
       </c>
       <c r="R26" t="n">
-        <v>6812190</v>
+        <v>6812077</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3246,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130307869</v>
+        <v>130307822</v>
       </c>
       <c r="B27" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3257,34 +3241,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444632</v>
+        <v>444627</v>
       </c>
       <c r="R27" t="n">
-        <v>6812157</v>
+        <v>6812121</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3343,10 +3335,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130307847</v>
+        <v>130307819</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>57849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,34 +3346,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444648</v>
+        <v>444481</v>
       </c>
       <c r="R28" t="n">
-        <v>6812167</v>
+        <v>6812067</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130307874</v>
+        <v>130307807</v>
       </c>
       <c r="B29" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,34 +3451,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444695</v>
+        <v>444566</v>
       </c>
       <c r="R29" t="n">
-        <v>6812170</v>
+        <v>6812030</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3537,10 +3545,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130307862</v>
+        <v>130307804</v>
       </c>
       <c r="B30" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3548,34 +3556,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444502</v>
+        <v>444506</v>
       </c>
       <c r="R30" t="n">
-        <v>6812091</v>
+        <v>6812034</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3634,10 +3650,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130307797</v>
+        <v>130307874</v>
       </c>
       <c r="B31" t="n">
-        <v>58011</v>
+        <v>79209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3645,42 +3661,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444480</v>
+        <v>444695</v>
       </c>
       <c r="R31" t="n">
-        <v>6812044</v>
+        <v>6812170</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3739,10 +3747,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130307827</v>
+        <v>130307862</v>
       </c>
       <c r="B32" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3750,42 +3758,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444700</v>
+        <v>444502</v>
       </c>
       <c r="R32" t="n">
-        <v>6812211</v>
+        <v>6812091</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130307807</v>
+        <v>130307827</v>
       </c>
       <c r="B33" t="n">
         <v>57849</v>
@@ -3877,7 +3877,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444566</v>
+        <v>444700</v>
       </c>
       <c r="R33" t="n">
-        <v>6812030</v>
+        <v>6812211</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130307804</v>
+        <v>130307797</v>
       </c>
       <c r="B34" t="n">
-        <v>57849</v>
+        <v>58011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3982,7 +3982,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444506</v>
+        <v>444480</v>
       </c>
       <c r="R34" t="n">
-        <v>6812034</v>
+        <v>6812044</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130307803</v>
+        <v>130307852</v>
       </c>
       <c r="B37" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4267,42 +4267,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444437</v>
+        <v>444645</v>
       </c>
       <c r="R37" t="n">
-        <v>6812004</v>
+        <v>6812074</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,10 +4353,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130307812</v>
+        <v>130307863</v>
       </c>
       <c r="B38" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,42 +4364,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444430</v>
+        <v>444505</v>
       </c>
       <c r="R38" t="n">
-        <v>6812075</v>
+        <v>6812061</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4466,10 +4450,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130307828</v>
+        <v>130307871</v>
       </c>
       <c r="B39" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4477,42 +4461,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444715</v>
+        <v>444705</v>
       </c>
       <c r="R39" t="n">
-        <v>6812217</v>
+        <v>6812214</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,7 +4547,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130307800</v>
+        <v>130307803</v>
       </c>
       <c r="B40" t="n">
         <v>57849</v>
@@ -4614,10 +4590,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444393</v>
+        <v>444437</v>
       </c>
       <c r="R40" t="n">
-        <v>6812026</v>
+        <v>6812004</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4676,7 +4652,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130307834</v>
+        <v>130307800</v>
       </c>
       <c r="B41" t="n">
         <v>57849</v>
@@ -4719,10 +4695,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444688</v>
+        <v>444393</v>
       </c>
       <c r="R41" t="n">
-        <v>6812170</v>
+        <v>6812026</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4781,10 +4757,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130307863</v>
+        <v>130307812</v>
       </c>
       <c r="B42" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4792,34 +4768,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444505</v>
+        <v>444430</v>
       </c>
       <c r="R42" t="n">
-        <v>6812061</v>
+        <v>6812075</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4878,10 +4862,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130307852</v>
+        <v>130307828</v>
       </c>
       <c r="B43" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4889,34 +4873,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444645</v>
+        <v>444715</v>
       </c>
       <c r="R43" t="n">
-        <v>6812074</v>
+        <v>6812217</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4975,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130307871</v>
+        <v>130307834</v>
       </c>
       <c r="B44" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4986,34 +4978,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444705</v>
+        <v>444688</v>
       </c>
       <c r="R44" t="n">
-        <v>6812214</v>
+        <v>6812170</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5266,7 +5266,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130307809</v>
+        <v>130307820</v>
       </c>
       <c r="B47" t="n">
         <v>57849</v>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444452</v>
+        <v>444459</v>
       </c>
       <c r="R47" t="n">
-        <v>6812004</v>
+        <v>6812090</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5371,7 +5371,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130307820</v>
+        <v>130307831</v>
       </c>
       <c r="B48" t="n">
         <v>57849</v>
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444459</v>
+        <v>444733</v>
       </c>
       <c r="R48" t="n">
-        <v>6812090</v>
+        <v>6812210</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5476,7 +5476,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130307831</v>
+        <v>130307809</v>
       </c>
       <c r="B49" t="n">
         <v>57849</v>
@@ -5519,10 +5519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444733</v>
+        <v>444452</v>
       </c>
       <c r="R49" t="n">
-        <v>6812210</v>
+        <v>6812004</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130307837</v>
+        <v>130307818</v>
       </c>
       <c r="B52" t="n">
         <v>57849</v>
@@ -5818,10 +5818,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444516</v>
+        <v>444484</v>
       </c>
       <c r="R52" t="n">
-        <v>6811948</v>
+        <v>6812056</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130307836</v>
+        <v>130307811</v>
       </c>
       <c r="B53" t="n">
         <v>57849</v>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444552</v>
+        <v>444426</v>
       </c>
       <c r="R53" t="n">
-        <v>6811979</v>
+        <v>6812079</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130307818</v>
+        <v>130307837</v>
       </c>
       <c r="B54" t="n">
         <v>57849</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444484</v>
+        <v>444516</v>
       </c>
       <c r="R54" t="n">
-        <v>6812056</v>
+        <v>6811948</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130307811</v>
+        <v>130307836</v>
       </c>
       <c r="B55" t="n">
         <v>57849</v>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444426</v>
+        <v>444552</v>
       </c>
       <c r="R55" t="n">
-        <v>6812079</v>
+        <v>6811979</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6405,7 +6405,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130307878</v>
+        <v>130307873</v>
       </c>
       <c r="B58" t="n">
         <v>79209</v>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444642</v>
+        <v>444714</v>
       </c>
       <c r="R58" t="n">
-        <v>6812075</v>
+        <v>6812206</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6502,10 +6502,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130307801</v>
+        <v>130307878</v>
       </c>
       <c r="B59" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,42 +6513,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444376</v>
+        <v>444642</v>
       </c>
       <c r="R59" t="n">
-        <v>6812020</v>
+        <v>6812075</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6607,10 +6599,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130307873</v>
+        <v>130307801</v>
       </c>
       <c r="B60" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6618,34 +6610,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444714</v>
+        <v>444376</v>
       </c>
       <c r="R60" t="n">
-        <v>6812206</v>
+        <v>6812020</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6809,7 +6809,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130307864</v>
+        <v>130307875</v>
       </c>
       <c r="B62" t="n">
         <v>79209</v>
@@ -6838,19 +6838,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444533</v>
+        <v>444676</v>
       </c>
       <c r="R62" t="n">
-        <v>6812085</v>
+        <v>6812126</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6891,7 +6888,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6910,7 +6906,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130307875</v>
+        <v>130307864</v>
       </c>
       <c r="B63" t="n">
         <v>79209</v>
@@ -6939,16 +6935,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444676</v>
+        <v>444533</v>
       </c>
       <c r="R63" t="n">
-        <v>6812126</v>
+        <v>6812085</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6989,6 +6988,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7112,10 +7112,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130307833</v>
+        <v>130307859</v>
       </c>
       <c r="B65" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7123,42 +7123,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444702</v>
+        <v>444491</v>
       </c>
       <c r="R65" t="n">
-        <v>6812194</v>
+        <v>6812073</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7217,7 +7209,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130307835</v>
+        <v>130307833</v>
       </c>
       <c r="B66" t="n">
         <v>57849</v>
@@ -7260,10 +7252,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444643</v>
+        <v>444702</v>
       </c>
       <c r="R66" t="n">
-        <v>6812117</v>
+        <v>6812194</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7322,7 +7314,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130307815</v>
+        <v>130307835</v>
       </c>
       <c r="B67" t="n">
         <v>57849</v>
@@ -7365,10 +7357,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444464</v>
+        <v>444643</v>
       </c>
       <c r="R67" t="n">
-        <v>6812074</v>
+        <v>6812117</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7427,10 +7419,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130307859</v>
+        <v>130307815</v>
       </c>
       <c r="B68" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7438,34 +7430,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444491</v>
+        <v>444464</v>
       </c>
       <c r="R68" t="n">
-        <v>6812073</v>
+        <v>6812074</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7629,45 +7629,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130307865</v>
+        <v>130307796</v>
       </c>
       <c r="B70" t="n">
-        <v>79209</v>
+        <v>57042</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444550</v>
+        <v>444508</v>
       </c>
       <c r="R70" t="n">
-        <v>6812103</v>
+        <v>6811946</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7700,6 +7708,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7726,53 +7739,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130307796</v>
+        <v>130307865</v>
       </c>
       <c r="B71" t="n">
-        <v>57042</v>
+        <v>79209</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444508</v>
+        <v>444550</v>
       </c>
       <c r="R71" t="n">
-        <v>6811946</v>
+        <v>6812103</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7805,11 +7810,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7941,45 +7941,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130307790</v>
+        <v>130307787</v>
       </c>
       <c r="B73" t="n">
-        <v>79828</v>
+        <v>91722</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444667</v>
+        <v>444683</v>
       </c>
       <c r="R73" t="n">
-        <v>6812191</v>
+        <v>6812180</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8020,6 +8023,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8135,48 +8139,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130307787</v>
+        <v>130307790</v>
       </c>
       <c r="B75" t="n">
-        <v>91721</v>
+        <v>79828</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444683</v>
+        <v>444667</v>
       </c>
       <c r="R75" t="n">
-        <v>6812180</v>
+        <v>6812191</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8217,7 +8218,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130307858</v>
+        <v>130307860</v>
       </c>
       <c r="B2" t="n">
         <v>79209</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444436</v>
+        <v>444487</v>
       </c>
       <c r="R2" t="n">
-        <v>6811920</v>
+        <v>6812030</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130307860</v>
+        <v>130307858</v>
       </c>
       <c r="B3" t="n">
         <v>79209</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444487</v>
+        <v>444436</v>
       </c>
       <c r="R3" t="n">
-        <v>6812030</v>
+        <v>6811920</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -974,53 +974,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130307845</v>
+        <v>130307876</v>
       </c>
       <c r="B5" t="n">
-        <v>98984</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444430</v>
+        <v>444651</v>
       </c>
       <c r="R5" t="n">
-        <v>6812024</v>
+        <v>6812124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1053,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1080,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130307839</v>
+        <v>130307850</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,42 +1082,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444522</v>
+        <v>444442</v>
       </c>
       <c r="R6" t="n">
-        <v>6811930</v>
+        <v>6811950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130307795</v>
+        <v>130307845</v>
       </c>
       <c r="B7" t="n">
-        <v>57042</v>
+        <v>98985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,31 +1179,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1228,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444500</v>
+        <v>444430</v>
       </c>
       <c r="R7" t="n">
-        <v>6812038</v>
+        <v>6812024</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,6 +1255,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1391,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130307876</v>
+        <v>130307825</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,34 +1386,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444651</v>
+        <v>444646</v>
       </c>
       <c r="R9" t="n">
-        <v>6812124</v>
+        <v>6812173</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,10 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130307850</v>
+        <v>130307814</v>
       </c>
       <c r="B10" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,34 +1491,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444442</v>
+        <v>444450</v>
       </c>
       <c r="R10" t="n">
-        <v>6811950</v>
+        <v>6812087</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130307825</v>
+        <v>130307839</v>
       </c>
       <c r="B11" t="n">
         <v>57849</v>
@@ -1618,7 +1618,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444646</v>
+        <v>444522</v>
       </c>
       <c r="R11" t="n">
-        <v>6812173</v>
+        <v>6811930</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,32 +1690,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130307814</v>
+        <v>130307795</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>57042</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444450</v>
+        <v>444500</v>
       </c>
       <c r="R12" t="n">
-        <v>6812087</v>
+        <v>6812038</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130307829</v>
+        <v>130307846</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,42 +2008,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444739</v>
+        <v>444569</v>
       </c>
       <c r="R15" t="n">
-        <v>6812234</v>
+        <v>6812062</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130307846</v>
+        <v>130307829</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,34 +2105,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444569</v>
+        <v>444739</v>
       </c>
       <c r="R16" t="n">
-        <v>6812062</v>
+        <v>6812234</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2304,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130307808</v>
+        <v>130307824</v>
       </c>
       <c r="B18" t="n">
         <v>57849</v>
@@ -2337,7 +2337,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444509</v>
+        <v>444617</v>
       </c>
       <c r="R18" t="n">
-        <v>6811987</v>
+        <v>6812150</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130307824</v>
+        <v>130307808</v>
       </c>
       <c r="B19" t="n">
         <v>57849</v>
@@ -2442,7 +2442,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444617</v>
+        <v>444509</v>
       </c>
       <c r="R19" t="n">
-        <v>6812150</v>
+        <v>6811987</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130307838</v>
+        <v>130307822</v>
       </c>
       <c r="B24" t="n">
         <v>57849</v>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444516</v>
+        <v>444627</v>
       </c>
       <c r="R24" t="n">
-        <v>6811940</v>
+        <v>6812121</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130307847</v>
+        <v>130307813</v>
       </c>
       <c r="B25" t="n">
-        <v>78967</v>
+        <v>57849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3039,34 +3039,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444648</v>
+        <v>444443</v>
       </c>
       <c r="R25" t="n">
-        <v>6812167</v>
+        <v>6812077</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,7 +3133,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130307813</v>
+        <v>130307819</v>
       </c>
       <c r="B26" t="n">
         <v>57849</v>
@@ -3168,10 +3176,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444443</v>
+        <v>444481</v>
       </c>
       <c r="R26" t="n">
-        <v>6812077</v>
+        <v>6812067</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,7 +3238,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130307822</v>
+        <v>130307838</v>
       </c>
       <c r="B27" t="n">
         <v>57849</v>
@@ -3273,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444627</v>
+        <v>444516</v>
       </c>
       <c r="R27" t="n">
-        <v>6812121</v>
+        <v>6811940</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3335,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130307819</v>
+        <v>130307847</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>78967</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3346,42 +3354,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444481</v>
+        <v>444648</v>
       </c>
       <c r="R28" t="n">
-        <v>6812067</v>
+        <v>6812167</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130307807</v>
+        <v>130307874</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,42 +3451,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444566</v>
+        <v>444695</v>
       </c>
       <c r="R29" t="n">
-        <v>6812030</v>
+        <v>6812170</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,10 +3537,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130307804</v>
+        <v>130307862</v>
       </c>
       <c r="B30" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3556,42 +3548,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444506</v>
+        <v>444502</v>
       </c>
       <c r="R30" t="n">
-        <v>6812034</v>
+        <v>6812091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3650,10 +3634,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130307874</v>
+        <v>130307827</v>
       </c>
       <c r="B31" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3661,34 +3645,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444695</v>
+        <v>444700</v>
       </c>
       <c r="R31" t="n">
-        <v>6812170</v>
+        <v>6812211</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3747,10 +3739,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130307862</v>
+        <v>130307807</v>
       </c>
       <c r="B32" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3758,34 +3750,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444502</v>
+        <v>444566</v>
       </c>
       <c r="R32" t="n">
-        <v>6812091</v>
+        <v>6812030</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130307827</v>
+        <v>130307804</v>
       </c>
       <c r="B33" t="n">
         <v>57849</v>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444700</v>
+        <v>444506</v>
       </c>
       <c r="R33" t="n">
-        <v>6812211</v>
+        <v>6812034</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130307852</v>
+        <v>130307863</v>
       </c>
       <c r="B37" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444645</v>
+        <v>444505</v>
       </c>
       <c r="R37" t="n">
-        <v>6812074</v>
+        <v>6812061</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130307863</v>
+        <v>130307871</v>
       </c>
       <c r="B38" t="n">
         <v>79209</v>
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444505</v>
+        <v>444705</v>
       </c>
       <c r="R38" t="n">
-        <v>6812061</v>
+        <v>6812214</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,10 +4450,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130307871</v>
+        <v>130307812</v>
       </c>
       <c r="B39" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4461,34 +4461,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444705</v>
+        <v>444430</v>
       </c>
       <c r="R39" t="n">
-        <v>6812214</v>
+        <v>6812075</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4547,7 +4555,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130307803</v>
+        <v>130307828</v>
       </c>
       <c r="B40" t="n">
         <v>57849</v>
@@ -4590,10 +4598,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444437</v>
+        <v>444715</v>
       </c>
       <c r="R40" t="n">
-        <v>6812004</v>
+        <v>6812217</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,7 +4660,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130307800</v>
+        <v>130307834</v>
       </c>
       <c r="B41" t="n">
         <v>57849</v>
@@ -4695,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444393</v>
+        <v>444688</v>
       </c>
       <c r="R41" t="n">
-        <v>6812026</v>
+        <v>6812170</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,7 +4765,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130307812</v>
+        <v>130307803</v>
       </c>
       <c r="B42" t="n">
         <v>57849</v>
@@ -4800,10 +4808,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444430</v>
+        <v>444437</v>
       </c>
       <c r="R42" t="n">
-        <v>6812075</v>
+        <v>6812004</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4862,7 +4870,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130307828</v>
+        <v>130307800</v>
       </c>
       <c r="B43" t="n">
         <v>57849</v>
@@ -4905,10 +4913,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444715</v>
+        <v>444393</v>
       </c>
       <c r="R43" t="n">
-        <v>6812217</v>
+        <v>6812026</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4967,10 +4975,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130307834</v>
+        <v>130307852</v>
       </c>
       <c r="B44" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4978,42 +4986,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444688</v>
+        <v>444645</v>
       </c>
       <c r="R44" t="n">
-        <v>6812170</v>
+        <v>6812074</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130307851</v>
+        <v>130307820</v>
       </c>
       <c r="B46" t="n">
-        <v>78966</v>
+        <v>57849</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,34 +5180,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444648</v>
+        <v>444459</v>
       </c>
       <c r="R46" t="n">
-        <v>6812167</v>
+        <v>6812090</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5266,10 +5274,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130307820</v>
+        <v>130307851</v>
       </c>
       <c r="B47" t="n">
-        <v>57849</v>
+        <v>78966</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5277,42 +5285,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444459</v>
+        <v>444648</v>
       </c>
       <c r="R47" t="n">
-        <v>6812090</v>
+        <v>6812167</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5371,7 +5371,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130307831</v>
+        <v>130307809</v>
       </c>
       <c r="B48" t="n">
         <v>57849</v>
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444733</v>
+        <v>444452</v>
       </c>
       <c r="R48" t="n">
-        <v>6812210</v>
+        <v>6812004</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5476,7 +5476,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130307809</v>
+        <v>130307831</v>
       </c>
       <c r="B49" t="n">
         <v>57849</v>
@@ -5519,10 +5519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444452</v>
+        <v>444733</v>
       </c>
       <c r="R49" t="n">
-        <v>6812004</v>
+        <v>6812210</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130307818</v>
+        <v>130307837</v>
       </c>
       <c r="B52" t="n">
         <v>57849</v>
@@ -5818,10 +5818,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444484</v>
+        <v>444516</v>
       </c>
       <c r="R52" t="n">
-        <v>6812056</v>
+        <v>6811948</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130307811</v>
+        <v>130307836</v>
       </c>
       <c r="B53" t="n">
         <v>57849</v>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444426</v>
+        <v>444552</v>
       </c>
       <c r="R53" t="n">
-        <v>6812079</v>
+        <v>6811979</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130307837</v>
+        <v>130307805</v>
       </c>
       <c r="B54" t="n">
         <v>57849</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444516</v>
+        <v>444669</v>
       </c>
       <c r="R54" t="n">
-        <v>6811948</v>
+        <v>6812147</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130307836</v>
+        <v>130307818</v>
       </c>
       <c r="B55" t="n">
         <v>57849</v>
@@ -6123,7 +6123,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444552</v>
+        <v>444484</v>
       </c>
       <c r="R55" t="n">
-        <v>6811979</v>
+        <v>6812056</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6195,7 +6195,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130307805</v>
+        <v>130307811</v>
       </c>
       <c r="B56" t="n">
         <v>57849</v>
@@ -6228,7 +6228,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444669</v>
+        <v>444426</v>
       </c>
       <c r="R56" t="n">
-        <v>6812147</v>
+        <v>6812079</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130307873</v>
+        <v>130307801</v>
       </c>
       <c r="B58" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6416,34 +6416,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444714</v>
+        <v>444376</v>
       </c>
       <c r="R58" t="n">
-        <v>6812206</v>
+        <v>6812020</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6502,10 +6510,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130307878</v>
+        <v>130307793</v>
       </c>
       <c r="B59" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,34 +6521,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444642</v>
+        <v>444496</v>
       </c>
       <c r="R59" t="n">
-        <v>6812075</v>
+        <v>6812068</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6599,10 +6615,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130307801</v>
+        <v>130307873</v>
       </c>
       <c r="B60" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6610,42 +6626,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444376</v>
+        <v>444714</v>
       </c>
       <c r="R60" t="n">
-        <v>6812020</v>
+        <v>6812206</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6704,10 +6712,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130307793</v>
+        <v>130307878</v>
       </c>
       <c r="B61" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6715,42 +6723,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444496</v>
+        <v>444642</v>
       </c>
       <c r="R61" t="n">
-        <v>6812068</v>
+        <v>6812075</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7209,7 +7209,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130307833</v>
+        <v>130307835</v>
       </c>
       <c r="B66" t="n">
         <v>57849</v>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444702</v>
+        <v>444643</v>
       </c>
       <c r="R66" t="n">
-        <v>6812194</v>
+        <v>6812117</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130307835</v>
+        <v>130307815</v>
       </c>
       <c r="B67" t="n">
         <v>57849</v>
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444643</v>
+        <v>444464</v>
       </c>
       <c r="R67" t="n">
-        <v>6812117</v>
+        <v>6812074</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7419,7 +7419,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130307815</v>
+        <v>130307833</v>
       </c>
       <c r="B68" t="n">
         <v>57849</v>
@@ -7462,10 +7462,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444464</v>
+        <v>444702</v>
       </c>
       <c r="R68" t="n">
-        <v>6812074</v>
+        <v>6812194</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7629,53 +7629,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130307796</v>
+        <v>130307865</v>
       </c>
       <c r="B70" t="n">
-        <v>57042</v>
+        <v>79209</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444508</v>
+        <v>444550</v>
       </c>
       <c r="R70" t="n">
-        <v>6811946</v>
+        <v>6812103</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7708,11 +7700,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7739,45 +7726,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130307865</v>
+        <v>130307796</v>
       </c>
       <c r="B71" t="n">
-        <v>79209</v>
+        <v>57042</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444550</v>
+        <v>444508</v>
       </c>
       <c r="R71" t="n">
-        <v>6812103</v>
+        <v>6811946</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7810,6 +7805,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7941,48 +7941,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130307787</v>
+        <v>130307790</v>
       </c>
       <c r="B73" t="n">
-        <v>91722</v>
+        <v>79828</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444683</v>
+        <v>444667</v>
       </c>
       <c r="R73" t="n">
-        <v>6812180</v>
+        <v>6812191</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8023,7 +8020,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8042,45 +8038,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130307868</v>
+        <v>130307787</v>
       </c>
       <c r="B74" t="n">
-        <v>79209</v>
+        <v>91723</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444623</v>
+        <v>444683</v>
       </c>
       <c r="R74" t="n">
-        <v>6812168</v>
+        <v>6812180</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8121,6 +8120,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8139,10 +8139,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130307790</v>
+        <v>130307868</v>
       </c>
       <c r="B75" t="n">
-        <v>79828</v>
+        <v>79209</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8150,21 +8150,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8174,10 +8174,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444667</v>
+        <v>444623</v>
       </c>
       <c r="R75" t="n">
-        <v>6812191</v>
+        <v>6812168</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130307860</v>
+        <v>130307858</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444487</v>
+        <v>444436</v>
       </c>
       <c r="R2" t="n">
-        <v>6812030</v>
+        <v>6811920</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130307858</v>
+        <v>130307860</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444436</v>
+        <v>444487</v>
       </c>
       <c r="R3" t="n">
-        <v>6811920</v>
+        <v>6812030</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>130307802</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130307876</v>
+        <v>130307867</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,16 +1003,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444651</v>
+        <v>444623</v>
       </c>
       <c r="R5" t="n">
-        <v>6812124</v>
+        <v>6812136</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,6 +1056,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1071,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130307850</v>
+        <v>130307876</v>
       </c>
       <c r="B6" t="n">
-        <v>78966</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,21 +1086,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444442</v>
+        <v>444651</v>
       </c>
       <c r="R6" t="n">
-        <v>6811950</v>
+        <v>6812124</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,53 +1172,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130307845</v>
+        <v>130307850</v>
       </c>
       <c r="B7" t="n">
-        <v>98985</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444430</v>
+        <v>444442</v>
       </c>
       <c r="R7" t="n">
-        <v>6812024</v>
+        <v>6811950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,7 +1251,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1274,10 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130307867</v>
+        <v>130307814</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1285,26 +1280,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444623</v>
+        <v>444450</v>
       </c>
       <c r="R8" t="n">
-        <v>6812136</v>
+        <v>6812087</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,7 +1356,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1375,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130307825</v>
+        <v>130307839</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1407,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1418,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444646</v>
+        <v>444522</v>
       </c>
       <c r="R9" t="n">
-        <v>6812173</v>
+        <v>6811930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,10 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130307814</v>
+        <v>130307825</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444450</v>
+        <v>444646</v>
       </c>
       <c r="R10" t="n">
-        <v>6812087</v>
+        <v>6812173</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130307839</v>
+        <v>130307795</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>57044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,7 +1617,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1628,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444522</v>
+        <v>444500</v>
       </c>
       <c r="R11" t="n">
-        <v>6811930</v>
+        <v>6812038</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,10 +1689,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130307795</v>
+        <v>130307845</v>
       </c>
       <c r="B12" t="n">
-        <v>57042</v>
+        <v>98987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,31 +1700,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1733,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444500</v>
+        <v>444430</v>
       </c>
       <c r="R12" t="n">
-        <v>6812038</v>
+        <v>6812024</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,6 +1776,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>130307840</v>
       </c>
       <c r="B13" t="n">
-        <v>57693</v>
+        <v>57695</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>130307789</v>
       </c>
       <c r="B14" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130307846</v>
+        <v>130307829</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>57851</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,34 +2008,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444569</v>
+        <v>444739</v>
       </c>
       <c r="R15" t="n">
-        <v>6812062</v>
+        <v>6812234</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130307829</v>
+        <v>130307846</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>78969</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2105,42 +2113,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444739</v>
+        <v>444569</v>
       </c>
       <c r="R16" t="n">
-        <v>6812234</v>
+        <v>6812062</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
         <v>130307817</v>
       </c>
       <c r="B17" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>130307824</v>
       </c>
       <c r="B18" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>130307808</v>
       </c>
       <c r="B19" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>130307810</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>130307843</v>
       </c>
       <c r="B21" t="n">
-        <v>57045</v>
+        <v>57047</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>130307870</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>130307869</v>
       </c>
       <c r="B23" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130307822</v>
+        <v>130307838</v>
       </c>
       <c r="B24" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444627</v>
+        <v>444516</v>
       </c>
       <c r="R24" t="n">
-        <v>6812121</v>
+        <v>6811940</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,7 +3031,7 @@
         <v>130307813</v>
       </c>
       <c r="B25" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130307819</v>
+        <v>130307822</v>
       </c>
       <c r="B26" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444481</v>
+        <v>444627</v>
       </c>
       <c r="R26" t="n">
-        <v>6812067</v>
+        <v>6812121</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,10 +3238,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130307838</v>
+        <v>130307819</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444516</v>
+        <v>444481</v>
       </c>
       <c r="R27" t="n">
-        <v>6811940</v>
+        <v>6812067</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,7 +3346,7 @@
         <v>130307847</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>130307874</v>
       </c>
       <c r="B29" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>130307862</v>
       </c>
       <c r="B30" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3634,10 +3634,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130307827</v>
+        <v>130307807</v>
       </c>
       <c r="B31" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444700</v>
+        <v>444566</v>
       </c>
       <c r="R31" t="n">
-        <v>6812211</v>
+        <v>6812030</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3739,10 +3739,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130307807</v>
+        <v>130307827</v>
       </c>
       <c r="B32" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444566</v>
+        <v>444700</v>
       </c>
       <c r="R32" t="n">
-        <v>6812030</v>
+        <v>6812211</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,7 +3847,7 @@
         <v>130307804</v>
       </c>
       <c r="B33" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>130307797</v>
       </c>
       <c r="B34" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>130307791</v>
       </c>
       <c r="B35" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>130307826</v>
       </c>
       <c r="B36" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>130307863</v>
       </c>
       <c r="B37" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130307871</v>
+        <v>130307852</v>
       </c>
       <c r="B38" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4364,21 +4364,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444705</v>
+        <v>444645</v>
       </c>
       <c r="R38" t="n">
-        <v>6812214</v>
+        <v>6812074</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,10 +4450,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130307812</v>
+        <v>130307871</v>
       </c>
       <c r="B39" t="n">
-        <v>57849</v>
+        <v>79211</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4461,42 +4461,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444430</v>
+        <v>444705</v>
       </c>
       <c r="R39" t="n">
-        <v>6812075</v>
+        <v>6812214</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4555,10 +4547,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130307828</v>
+        <v>130307812</v>
       </c>
       <c r="B40" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4598,10 +4590,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444715</v>
+        <v>444430</v>
       </c>
       <c r="R40" t="n">
-        <v>6812217</v>
+        <v>6812075</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4660,10 +4652,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130307834</v>
+        <v>130307800</v>
       </c>
       <c r="B41" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4703,10 +4695,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444688</v>
+        <v>444393</v>
       </c>
       <c r="R41" t="n">
-        <v>6812170</v>
+        <v>6812026</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4765,10 +4757,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130307803</v>
+        <v>130307834</v>
       </c>
       <c r="B42" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4808,10 +4800,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444437</v>
+        <v>444688</v>
       </c>
       <c r="R42" t="n">
-        <v>6812004</v>
+        <v>6812170</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,10 +4862,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130307800</v>
+        <v>130307803</v>
       </c>
       <c r="B43" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4913,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444393</v>
+        <v>444437</v>
       </c>
       <c r="R43" t="n">
-        <v>6812026</v>
+        <v>6812004</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4975,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130307852</v>
+        <v>130307828</v>
       </c>
       <c r="B44" t="n">
-        <v>78966</v>
+        <v>57851</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4986,34 +4978,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444645</v>
+        <v>444715</v>
       </c>
       <c r="R44" t="n">
-        <v>6812074</v>
+        <v>6812217</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5075,7 +5075,7 @@
         <v>130307877</v>
       </c>
       <c r="B45" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130307820</v>
+        <v>130307851</v>
       </c>
       <c r="B46" t="n">
-        <v>57849</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,42 +5180,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444459</v>
+        <v>444648</v>
       </c>
       <c r="R46" t="n">
-        <v>6812090</v>
+        <v>6812167</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5274,10 +5266,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130307851</v>
+        <v>130307809</v>
       </c>
       <c r="B47" t="n">
-        <v>78966</v>
+        <v>57851</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5285,34 +5277,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444648</v>
+        <v>444452</v>
       </c>
       <c r="R47" t="n">
-        <v>6812167</v>
+        <v>6812004</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130307809</v>
+        <v>130307820</v>
       </c>
       <c r="B48" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444452</v>
+        <v>444459</v>
       </c>
       <c r="R48" t="n">
-        <v>6812004</v>
+        <v>6812090</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5479,7 +5479,7 @@
         <v>130307831</v>
       </c>
       <c r="B49" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>130307866</v>
       </c>
       <c r="B50" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>130307861</v>
       </c>
       <c r="B51" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>130307837</v>
       </c>
       <c r="B52" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>130307836</v>
       </c>
       <c r="B53" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5985,10 +5985,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130307805</v>
+        <v>130307818</v>
       </c>
       <c r="B54" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444669</v>
+        <v>444484</v>
       </c>
       <c r="R54" t="n">
-        <v>6812147</v>
+        <v>6812056</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,10 +6090,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130307818</v>
+        <v>130307805</v>
       </c>
       <c r="B55" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444484</v>
+        <v>444669</v>
       </c>
       <c r="R55" t="n">
-        <v>6812056</v>
+        <v>6812147</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6198,7 +6198,7 @@
         <v>130307811</v>
       </c>
       <c r="B56" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>130307823</v>
       </c>
       <c r="B57" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>130307801</v>
       </c>
       <c r="B58" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6510,10 +6510,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130307793</v>
+        <v>130307873</v>
       </c>
       <c r="B59" t="n">
-        <v>57852</v>
+        <v>79211</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6521,42 +6521,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444496</v>
+        <v>444714</v>
       </c>
       <c r="R59" t="n">
-        <v>6812068</v>
+        <v>6812206</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6615,10 +6607,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130307873</v>
+        <v>130307878</v>
       </c>
       <c r="B60" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6650,10 +6642,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444714</v>
+        <v>444642</v>
       </c>
       <c r="R60" t="n">
-        <v>6812206</v>
+        <v>6812075</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6712,10 +6704,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130307878</v>
+        <v>130307793</v>
       </c>
       <c r="B61" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6723,34 +6715,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444642</v>
+        <v>444496</v>
       </c>
       <c r="R61" t="n">
-        <v>6812075</v>
+        <v>6812068</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
         <v>130307875</v>
       </c>
       <c r="B62" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>130307864</v>
       </c>
       <c r="B63" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>130307806</v>
       </c>
       <c r="B64" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>130307859</v>
       </c>
       <c r="B65" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130307835</v>
+        <v>130307833</v>
       </c>
       <c r="B66" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444643</v>
+        <v>444702</v>
       </c>
       <c r="R66" t="n">
-        <v>6812117</v>
+        <v>6812194</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7314,10 +7314,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130307815</v>
+        <v>130307835</v>
       </c>
       <c r="B67" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7357,10 +7357,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444464</v>
+        <v>444643</v>
       </c>
       <c r="R67" t="n">
-        <v>6812074</v>
+        <v>6812117</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7419,10 +7419,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130307833</v>
+        <v>130307815</v>
       </c>
       <c r="B68" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7462,10 +7462,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444702</v>
+        <v>444464</v>
       </c>
       <c r="R68" t="n">
-        <v>6812194</v>
+        <v>6812074</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7527,7 +7527,7 @@
         <v>130307832</v>
       </c>
       <c r="B69" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>130307865</v>
       </c>
       <c r="B70" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>130307796</v>
       </c>
       <c r="B71" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>130307821</v>
       </c>
       <c r="B72" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>130307790</v>
       </c>
       <c r="B73" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>130307787</v>
       </c>
       <c r="B74" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>130307868</v>
       </c>
       <c r="B75" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130307858</v>
+        <v>130307802</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444436</v>
+        <v>444397</v>
       </c>
       <c r="R2" t="n">
-        <v>6811920</v>
+        <v>6812004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130307860</v>
+        <v>130307858</v>
       </c>
       <c r="B3" t="n">
         <v>79211</v>
@@ -807,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444487</v>
+        <v>444436</v>
       </c>
       <c r="R3" t="n">
-        <v>6812030</v>
+        <v>6811920</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130307802</v>
+        <v>130307860</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444397</v>
+        <v>444487</v>
       </c>
       <c r="R4" t="n">
-        <v>6812004</v>
+        <v>6812030</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130307867</v>
+        <v>130307839</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,26 +985,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1012,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444623</v>
+        <v>444522</v>
       </c>
       <c r="R5" t="n">
-        <v>6812136</v>
+        <v>6811930</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1061,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1075,7 +1079,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130307876</v>
+        <v>130307867</v>
       </c>
       <c r="B6" t="n">
         <v>79211</v>
@@ -1104,16 +1108,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444651</v>
+        <v>444623</v>
       </c>
       <c r="R6" t="n">
-        <v>6812124</v>
+        <v>6812136</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,6 +1161,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1172,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130307850</v>
+        <v>130307876</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1207,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444442</v>
+        <v>444651</v>
       </c>
       <c r="R7" t="n">
-        <v>6811950</v>
+        <v>6812124</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130307814</v>
+        <v>130307850</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,42 +1288,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444450</v>
+        <v>444442</v>
       </c>
       <c r="R8" t="n">
-        <v>6812087</v>
+        <v>6811950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130307839</v>
+        <v>130307825</v>
       </c>
       <c r="B9" t="n">
         <v>57851</v>
@@ -1407,7 +1407,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444522</v>
+        <v>444646</v>
       </c>
       <c r="R9" t="n">
-        <v>6811930</v>
+        <v>6812173</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130307825</v>
+        <v>130307814</v>
       </c>
       <c r="B10" t="n">
         <v>57851</v>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444646</v>
+        <v>444450</v>
       </c>
       <c r="R10" t="n">
-        <v>6812173</v>
+        <v>6812087</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,7 +1692,7 @@
         <v>130307845</v>
       </c>
       <c r="B12" t="n">
-        <v>98987</v>
+        <v>98991</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130307789</v>
+        <v>130307829</v>
       </c>
       <c r="B14" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,34 +1911,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444433</v>
+        <v>444739</v>
       </c>
       <c r="R14" t="n">
-        <v>6811944</v>
+        <v>6812234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130307829</v>
+        <v>130307789</v>
       </c>
       <c r="B15" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,42 +2016,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444739</v>
+        <v>444433</v>
       </c>
       <c r="R15" t="n">
-        <v>6812234</v>
+        <v>6811944</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2304,7 +2304,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130307824</v>
+        <v>130307810</v>
       </c>
       <c r="B18" t="n">
         <v>57851</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444617</v>
+        <v>444410</v>
       </c>
       <c r="R18" t="n">
-        <v>6812150</v>
+        <v>6812061</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,27 +2409,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130307808</v>
+        <v>130307843</v>
       </c>
       <c r="B19" t="n">
-        <v>57851</v>
+        <v>57047</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2442,7 +2442,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444509</v>
+        <v>444721</v>
       </c>
       <c r="R19" t="n">
-        <v>6811987</v>
+        <v>6812209</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2488,6 +2488,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2514,7 +2519,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130307810</v>
+        <v>130307824</v>
       </c>
       <c r="B20" t="n">
         <v>57851</v>
@@ -2557,10 +2562,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444410</v>
+        <v>444617</v>
       </c>
       <c r="R20" t="n">
-        <v>6812061</v>
+        <v>6812150</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2619,27 +2624,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130307843</v>
+        <v>130307808</v>
       </c>
       <c r="B21" t="n">
-        <v>57047</v>
+        <v>57851</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2652,7 +2657,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2662,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444721</v>
+        <v>444509</v>
       </c>
       <c r="R21" t="n">
-        <v>6812209</v>
+        <v>6811987</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2698,11 +2703,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2729,10 +2729,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130307870</v>
+        <v>130307847</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444659</v>
+        <v>444648</v>
       </c>
       <c r="R22" t="n">
-        <v>6812190</v>
+        <v>6812167</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,7 +2826,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130307869</v>
+        <v>130307870</v>
       </c>
       <c r="B23" t="n">
         <v>79211</v>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444632</v>
+        <v>444659</v>
       </c>
       <c r="R23" t="n">
-        <v>6812157</v>
+        <v>6812190</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130307838</v>
+        <v>130307869</v>
       </c>
       <c r="B24" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2934,42 +2934,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444516</v>
+        <v>444632</v>
       </c>
       <c r="R24" t="n">
-        <v>6811940</v>
+        <v>6812157</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3343,10 +3335,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130307847</v>
+        <v>130307838</v>
       </c>
       <c r="B28" t="n">
-        <v>78969</v>
+        <v>57851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,34 +3346,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444648</v>
+        <v>444516</v>
       </c>
       <c r="R28" t="n">
-        <v>6812167</v>
+        <v>6811940</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130307807</v>
+        <v>130307827</v>
       </c>
       <c r="B31" t="n">
         <v>57851</v>
@@ -3667,7 +3667,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444566</v>
+        <v>444700</v>
       </c>
       <c r="R31" t="n">
-        <v>6812030</v>
+        <v>6812211</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130307827</v>
+        <v>130307807</v>
       </c>
       <c r="B32" t="n">
         <v>57851</v>
@@ -3772,7 +3772,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444700</v>
+        <v>444566</v>
       </c>
       <c r="R32" t="n">
-        <v>6812211</v>
+        <v>6812030</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130307804</v>
+        <v>130307797</v>
       </c>
       <c r="B33" t="n">
-        <v>57851</v>
+        <v>58013</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,7 +3877,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444506</v>
+        <v>444480</v>
       </c>
       <c r="R33" t="n">
-        <v>6812034</v>
+        <v>6812044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130307797</v>
+        <v>130307804</v>
       </c>
       <c r="B34" t="n">
-        <v>58013</v>
+        <v>57851</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3982,7 +3982,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444480</v>
+        <v>444506</v>
       </c>
       <c r="R34" t="n">
-        <v>6812044</v>
+        <v>6812034</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130307812</v>
+        <v>130307828</v>
       </c>
       <c r="B40" t="n">
         <v>57851</v>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444430</v>
+        <v>444715</v>
       </c>
       <c r="R40" t="n">
-        <v>6812075</v>
+        <v>6812217</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4757,7 +4757,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130307834</v>
+        <v>130307803</v>
       </c>
       <c r="B42" t="n">
         <v>57851</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444688</v>
+        <v>444437</v>
       </c>
       <c r="R42" t="n">
-        <v>6812170</v>
+        <v>6812004</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4862,7 +4862,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130307803</v>
+        <v>130307812</v>
       </c>
       <c r="B43" t="n">
         <v>57851</v>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444437</v>
+        <v>444430</v>
       </c>
       <c r="R43" t="n">
-        <v>6812004</v>
+        <v>6812075</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4967,7 +4967,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130307828</v>
+        <v>130307834</v>
       </c>
       <c r="B44" t="n">
         <v>57851</v>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444715</v>
+        <v>444688</v>
       </c>
       <c r="R44" t="n">
-        <v>6812217</v>
+        <v>6812170</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130307877</v>
+        <v>130307831</v>
       </c>
       <c r="B45" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,34 +5083,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444661</v>
+        <v>444733</v>
       </c>
       <c r="R45" t="n">
-        <v>6812100</v>
+        <v>6812210</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5169,10 +5177,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130307851</v>
+        <v>130307877</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,21 +5188,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5204,10 +5212,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444648</v>
+        <v>444661</v>
       </c>
       <c r="R46" t="n">
-        <v>6812167</v>
+        <v>6812100</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5266,10 +5274,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130307809</v>
+        <v>130307851</v>
       </c>
       <c r="B47" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5277,42 +5285,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444452</v>
+        <v>444648</v>
       </c>
       <c r="R47" t="n">
-        <v>6812004</v>
+        <v>6812167</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5371,7 +5371,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130307820</v>
+        <v>130307809</v>
       </c>
       <c r="B48" t="n">
         <v>57851</v>
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444459</v>
+        <v>444452</v>
       </c>
       <c r="R48" t="n">
-        <v>6812090</v>
+        <v>6812004</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5476,7 +5476,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130307831</v>
+        <v>130307820</v>
       </c>
       <c r="B49" t="n">
         <v>57851</v>
@@ -5519,10 +5519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444733</v>
+        <v>444459</v>
       </c>
       <c r="R49" t="n">
-        <v>6812210</v>
+        <v>6812090</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5581,10 +5581,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130307866</v>
+        <v>130307805</v>
       </c>
       <c r="B50" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5592,34 +5592,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444583</v>
+        <v>444669</v>
       </c>
       <c r="R50" t="n">
-        <v>6812106</v>
+        <v>6812147</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5678,10 +5686,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130307861</v>
+        <v>130307811</v>
       </c>
       <c r="B51" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5689,34 +5697,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444477</v>
+        <v>444426</v>
       </c>
       <c r="R51" t="n">
-        <v>6812077</v>
+        <v>6812079</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5791,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130307837</v>
+        <v>130307866</v>
       </c>
       <c r="B52" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5786,42 +5802,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444516</v>
+        <v>444583</v>
       </c>
       <c r="R52" t="n">
-        <v>6811948</v>
+        <v>6812106</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5880,10 +5888,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130307836</v>
+        <v>130307861</v>
       </c>
       <c r="B53" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5891,42 +5899,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444552</v>
+        <v>444477</v>
       </c>
       <c r="R53" t="n">
-        <v>6811979</v>
+        <v>6812077</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130307818</v>
+        <v>130307837</v>
       </c>
       <c r="B54" t="n">
         <v>57851</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444484</v>
+        <v>444516</v>
       </c>
       <c r="R54" t="n">
-        <v>6812056</v>
+        <v>6811948</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130307805</v>
+        <v>130307836</v>
       </c>
       <c r="B55" t="n">
         <v>57851</v>
@@ -6123,7 +6123,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444669</v>
+        <v>444552</v>
       </c>
       <c r="R55" t="n">
-        <v>6812147</v>
+        <v>6811979</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6195,7 +6195,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130307811</v>
+        <v>130307818</v>
       </c>
       <c r="B56" t="n">
         <v>57851</v>
@@ -6228,7 +6228,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444426</v>
+        <v>444484</v>
       </c>
       <c r="R56" t="n">
-        <v>6812079</v>
+        <v>6812056</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130307801</v>
+        <v>130307873</v>
       </c>
       <c r="B58" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6416,42 +6416,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444376</v>
+        <v>444714</v>
       </c>
       <c r="R58" t="n">
-        <v>6812020</v>
+        <v>6812206</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6510,7 +6502,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130307873</v>
+        <v>130307878</v>
       </c>
       <c r="B59" t="n">
         <v>79211</v>
@@ -6545,10 +6537,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444714</v>
+        <v>444642</v>
       </c>
       <c r="R59" t="n">
-        <v>6812206</v>
+        <v>6812075</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6607,10 +6599,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130307878</v>
+        <v>130307801</v>
       </c>
       <c r="B60" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6618,34 +6610,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444642</v>
+        <v>444376</v>
       </c>
       <c r="R60" t="n">
-        <v>6812075</v>
+        <v>6812020</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7112,10 +7112,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130307859</v>
+        <v>130307835</v>
       </c>
       <c r="B65" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7123,34 +7123,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444491</v>
+        <v>444643</v>
       </c>
       <c r="R65" t="n">
-        <v>6812073</v>
+        <v>6812117</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7209,7 +7217,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130307833</v>
+        <v>130307815</v>
       </c>
       <c r="B66" t="n">
         <v>57851</v>
@@ -7252,10 +7260,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444702</v>
+        <v>444464</v>
       </c>
       <c r="R66" t="n">
-        <v>6812194</v>
+        <v>6812074</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7314,10 +7322,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130307835</v>
+        <v>130307859</v>
       </c>
       <c r="B67" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7325,42 +7333,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444643</v>
+        <v>444491</v>
       </c>
       <c r="R67" t="n">
-        <v>6812117</v>
+        <v>6812073</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7419,7 +7419,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130307815</v>
+        <v>130307833</v>
       </c>
       <c r="B68" t="n">
         <v>57851</v>
@@ -7462,10 +7462,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444464</v>
+        <v>444702</v>
       </c>
       <c r="R68" t="n">
-        <v>6812074</v>
+        <v>6812194</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8038,48 +8038,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130307787</v>
+        <v>130307868</v>
       </c>
       <c r="B74" t="n">
-        <v>91725</v>
+        <v>79211</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444683</v>
+        <v>444623</v>
       </c>
       <c r="R74" t="n">
-        <v>6812180</v>
+        <v>6812168</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8120,7 +8117,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8139,45 +8135,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130307868</v>
+        <v>130307787</v>
       </c>
       <c r="B75" t="n">
-        <v>79211</v>
+        <v>91725</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444623</v>
+        <v>444683</v>
       </c>
       <c r="R75" t="n">
-        <v>6812168</v>
+        <v>6812180</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8218,6 +8217,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130307839</v>
+        <v>130307867</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,31 +985,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1017,10 +1012,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444522</v>
+        <v>444623</v>
       </c>
       <c r="R5" t="n">
-        <v>6811930</v>
+        <v>6812136</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,6 +1056,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1079,7 +1075,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130307867</v>
+        <v>130307876</v>
       </c>
       <c r="B6" t="n">
         <v>79211</v>
@@ -1108,19 +1104,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444623</v>
+        <v>444651</v>
       </c>
       <c r="R6" t="n">
-        <v>6812136</v>
+        <v>6812124</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,7 +1154,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1180,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130307876</v>
+        <v>130307850</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1183,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444651</v>
+        <v>444442</v>
       </c>
       <c r="R7" t="n">
-        <v>6812124</v>
+        <v>6811950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,10 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130307850</v>
+        <v>130307814</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,34 +1280,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444442</v>
+        <v>444450</v>
       </c>
       <c r="R8" t="n">
-        <v>6811950</v>
+        <v>6812087</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130307825</v>
+        <v>130307795</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444646</v>
+        <v>444500</v>
       </c>
       <c r="R9" t="n">
-        <v>6812173</v>
+        <v>6812038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,42 +1479,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130307814</v>
+        <v>130307845</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>98991</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444450</v>
+        <v>444430</v>
       </c>
       <c r="R10" t="n">
-        <v>6812087</v>
+        <v>6812024</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,6 +1566,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1584,32 +1585,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130307795</v>
+        <v>130307839</v>
       </c>
       <c r="B11" t="n">
-        <v>57044</v>
+        <v>57851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1617,7 +1618,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1627,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444500</v>
+        <v>444522</v>
       </c>
       <c r="R11" t="n">
-        <v>6812038</v>
+        <v>6811930</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,42 +1690,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130307845</v>
+        <v>130307825</v>
       </c>
       <c r="B12" t="n">
-        <v>98991</v>
+        <v>57851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1732,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444430</v>
+        <v>444646</v>
       </c>
       <c r="R12" t="n">
-        <v>6812024</v>
+        <v>6812173</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,7 +1777,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130307829</v>
+        <v>130307789</v>
       </c>
       <c r="B14" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,42 +1911,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444739</v>
+        <v>444433</v>
       </c>
       <c r="R14" t="n">
-        <v>6812234</v>
+        <v>6811944</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130307789</v>
+        <v>130307829</v>
       </c>
       <c r="B15" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,34 +2008,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444433</v>
+        <v>444739</v>
       </c>
       <c r="R15" t="n">
-        <v>6811944</v>
+        <v>6812234</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2304,7 +2304,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130307810</v>
+        <v>130307824</v>
       </c>
       <c r="B18" t="n">
         <v>57851</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444410</v>
+        <v>444617</v>
       </c>
       <c r="R18" t="n">
-        <v>6812061</v>
+        <v>6812150</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,27 +2409,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130307843</v>
+        <v>130307808</v>
       </c>
       <c r="B19" t="n">
-        <v>57047</v>
+        <v>57851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2442,7 +2442,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444721</v>
+        <v>444509</v>
       </c>
       <c r="R19" t="n">
-        <v>6812209</v>
+        <v>6811987</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2488,11 +2488,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2519,7 +2514,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130307824</v>
+        <v>130307810</v>
       </c>
       <c r="B20" t="n">
         <v>57851</v>
@@ -2562,10 +2557,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444617</v>
+        <v>444410</v>
       </c>
       <c r="R20" t="n">
-        <v>6812150</v>
+        <v>6812061</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2624,27 +2619,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130307808</v>
+        <v>130307843</v>
       </c>
       <c r="B21" t="n">
-        <v>57851</v>
+        <v>57047</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2657,7 +2652,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2667,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444509</v>
+        <v>444721</v>
       </c>
       <c r="R21" t="n">
-        <v>6811987</v>
+        <v>6812209</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,6 +2698,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2729,10 +2729,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130307847</v>
+        <v>130307870</v>
       </c>
       <c r="B22" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444648</v>
+        <v>444659</v>
       </c>
       <c r="R22" t="n">
-        <v>6812167</v>
+        <v>6812190</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,7 +2826,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130307870</v>
+        <v>130307869</v>
       </c>
       <c r="B23" t="n">
         <v>79211</v>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444659</v>
+        <v>444632</v>
       </c>
       <c r="R23" t="n">
-        <v>6812190</v>
+        <v>6812157</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130307869</v>
+        <v>130307819</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2934,34 +2934,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444632</v>
+        <v>444481</v>
       </c>
       <c r="R24" t="n">
-        <v>6812157</v>
+        <v>6812067</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,7 +3238,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130307819</v>
+        <v>130307838</v>
       </c>
       <c r="B27" t="n">
         <v>57851</v>
@@ -3273,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444481</v>
+        <v>444516</v>
       </c>
       <c r="R27" t="n">
-        <v>6812067</v>
+        <v>6811940</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3335,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130307838</v>
+        <v>130307847</v>
       </c>
       <c r="B28" t="n">
-        <v>57851</v>
+        <v>78969</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3346,42 +3354,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444516</v>
+        <v>444648</v>
       </c>
       <c r="R28" t="n">
-        <v>6811940</v>
+        <v>6812167</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130307797</v>
+        <v>130307804</v>
       </c>
       <c r="B33" t="n">
-        <v>58013</v>
+        <v>57851</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,7 +3877,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444480</v>
+        <v>444506</v>
       </c>
       <c r="R33" t="n">
-        <v>6812044</v>
+        <v>6812034</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130307804</v>
+        <v>130307797</v>
       </c>
       <c r="B34" t="n">
-        <v>57851</v>
+        <v>58013</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3982,7 +3982,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444506</v>
+        <v>444480</v>
       </c>
       <c r="R34" t="n">
-        <v>6812034</v>
+        <v>6812044</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130307791</v>
+        <v>130307826</v>
       </c>
       <c r="B35" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4065,34 +4065,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444608</v>
+        <v>444689</v>
       </c>
       <c r="R35" t="n">
-        <v>6812061</v>
+        <v>6812204</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4151,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130307826</v>
+        <v>130307791</v>
       </c>
       <c r="B36" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4162,42 +4170,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444689</v>
+        <v>444608</v>
       </c>
       <c r="R36" t="n">
-        <v>6812204</v>
+        <v>6812061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130307828</v>
+        <v>130307803</v>
       </c>
       <c r="B40" t="n">
         <v>57851</v>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444715</v>
+        <v>444437</v>
       </c>
       <c r="R40" t="n">
-        <v>6812217</v>
+        <v>6812004</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,7 +4652,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130307800</v>
+        <v>130307812</v>
       </c>
       <c r="B41" t="n">
         <v>57851</v>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444393</v>
+        <v>444430</v>
       </c>
       <c r="R41" t="n">
-        <v>6812026</v>
+        <v>6812075</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,7 +4757,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130307803</v>
+        <v>130307828</v>
       </c>
       <c r="B42" t="n">
         <v>57851</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444437</v>
+        <v>444715</v>
       </c>
       <c r="R42" t="n">
-        <v>6812004</v>
+        <v>6812217</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4862,7 +4862,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130307812</v>
+        <v>130307800</v>
       </c>
       <c r="B43" t="n">
         <v>57851</v>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444430</v>
+        <v>444393</v>
       </c>
       <c r="R43" t="n">
-        <v>6812075</v>
+        <v>6812026</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130307831</v>
+        <v>130307877</v>
       </c>
       <c r="B45" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,42 +5083,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444733</v>
+        <v>444661</v>
       </c>
       <c r="R45" t="n">
-        <v>6812210</v>
+        <v>6812100</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5177,10 +5169,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130307877</v>
+        <v>130307851</v>
       </c>
       <c r="B46" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5188,21 +5180,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5212,10 +5204,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444661</v>
+        <v>444648</v>
       </c>
       <c r="R46" t="n">
-        <v>6812100</v>
+        <v>6812167</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5274,10 +5266,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130307851</v>
+        <v>130307809</v>
       </c>
       <c r="B47" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5285,34 +5277,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444648</v>
+        <v>444452</v>
       </c>
       <c r="R47" t="n">
-        <v>6812167</v>
+        <v>6812004</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5371,7 +5371,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130307809</v>
+        <v>130307820</v>
       </c>
       <c r="B48" t="n">
         <v>57851</v>
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444452</v>
+        <v>444459</v>
       </c>
       <c r="R48" t="n">
-        <v>6812004</v>
+        <v>6812090</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5476,7 +5476,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130307820</v>
+        <v>130307831</v>
       </c>
       <c r="B49" t="n">
         <v>57851</v>
@@ -5519,10 +5519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444459</v>
+        <v>444733</v>
       </c>
       <c r="R49" t="n">
-        <v>6812090</v>
+        <v>6812210</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5581,10 +5581,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130307805</v>
+        <v>130307866</v>
       </c>
       <c r="B50" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5592,42 +5592,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444669</v>
+        <v>444583</v>
       </c>
       <c r="R50" t="n">
-        <v>6812147</v>
+        <v>6812106</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5686,10 +5678,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130307811</v>
+        <v>130307861</v>
       </c>
       <c r="B51" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5697,42 +5689,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444426</v>
+        <v>444477</v>
       </c>
       <c r="R51" t="n">
-        <v>6812079</v>
+        <v>6812077</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5791,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130307866</v>
+        <v>130307837</v>
       </c>
       <c r="B52" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5802,34 +5786,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444583</v>
+        <v>444516</v>
       </c>
       <c r="R52" t="n">
-        <v>6812106</v>
+        <v>6811948</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5888,10 +5880,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130307861</v>
+        <v>130307811</v>
       </c>
       <c r="B53" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5899,34 +5891,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444477</v>
+        <v>444426</v>
       </c>
       <c r="R53" t="n">
-        <v>6812077</v>
+        <v>6812079</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130307837</v>
+        <v>130307805</v>
       </c>
       <c r="B54" t="n">
         <v>57851</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444516</v>
+        <v>444669</v>
       </c>
       <c r="R54" t="n">
-        <v>6811948</v>
+        <v>6812147</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130307875</v>
+        <v>130307806</v>
       </c>
       <c r="B62" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6820,34 +6820,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444676</v>
+        <v>444656</v>
       </c>
       <c r="R62" t="n">
-        <v>6812126</v>
+        <v>6812108</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6906,7 +6914,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130307864</v>
+        <v>130307875</v>
       </c>
       <c r="B63" t="n">
         <v>79211</v>
@@ -6935,19 +6943,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444533</v>
+        <v>444676</v>
       </c>
       <c r="R63" t="n">
-        <v>6812085</v>
+        <v>6812126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6988,7 +6993,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7007,10 +7011,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130307806</v>
+        <v>130307864</v>
       </c>
       <c r="B64" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7018,31 +7022,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7050,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444656</v>
+        <v>444533</v>
       </c>
       <c r="R64" t="n">
-        <v>6812108</v>
+        <v>6812085</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7094,6 +7093,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7112,7 +7112,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130307835</v>
+        <v>130307833</v>
       </c>
       <c r="B65" t="n">
         <v>57851</v>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444643</v>
+        <v>444702</v>
       </c>
       <c r="R65" t="n">
-        <v>6812117</v>
+        <v>6812194</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130307815</v>
+        <v>130307835</v>
       </c>
       <c r="B66" t="n">
         <v>57851</v>
@@ -7260,10 +7260,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444464</v>
+        <v>444643</v>
       </c>
       <c r="R66" t="n">
-        <v>6812074</v>
+        <v>6812117</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7322,10 +7322,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130307859</v>
+        <v>130307815</v>
       </c>
       <c r="B67" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7333,34 +7333,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444491</v>
+        <v>444464</v>
       </c>
       <c r="R67" t="n">
-        <v>6812073</v>
+        <v>6812074</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7419,10 +7427,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130307833</v>
+        <v>130307859</v>
       </c>
       <c r="B68" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7430,42 +7438,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444702</v>
+        <v>444491</v>
       </c>
       <c r="R68" t="n">
-        <v>6812194</v>
+        <v>6812073</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7941,10 +7941,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130307790</v>
+        <v>130307868</v>
       </c>
       <c r="B73" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7952,21 +7952,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7976,10 +7976,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444667</v>
+        <v>444623</v>
       </c>
       <c r="R73" t="n">
-        <v>6812191</v>
+        <v>6812168</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8038,45 +8038,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130307868</v>
+        <v>130307787</v>
       </c>
       <c r="B74" t="n">
-        <v>79211</v>
+        <v>91725</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444623</v>
+        <v>444683</v>
       </c>
       <c r="R74" t="n">
-        <v>6812168</v>
+        <v>6812180</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8117,6 +8120,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8135,48 +8139,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130307787</v>
+        <v>130307790</v>
       </c>
       <c r="B75" t="n">
-        <v>91725</v>
+        <v>79830</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444683</v>
+        <v>444667</v>
       </c>
       <c r="R75" t="n">
-        <v>6812180</v>
+        <v>6812191</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8217,7 +8218,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130307802</v>
+        <v>130307858</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444397</v>
+        <v>444436</v>
       </c>
       <c r="R2" t="n">
-        <v>6812004</v>
+        <v>6811920</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130307858</v>
+        <v>130307860</v>
       </c>
       <c r="B3" t="n">
         <v>79211</v>
@@ -815,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444436</v>
+        <v>444487</v>
       </c>
       <c r="R3" t="n">
-        <v>6811920</v>
+        <v>6812030</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130307860</v>
+        <v>130307802</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444487</v>
+        <v>444397</v>
       </c>
       <c r="R4" t="n">
-        <v>6812030</v>
+        <v>6812004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130307867</v>
+        <v>130307839</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,26 +985,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1012,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444623</v>
+        <v>444522</v>
       </c>
       <c r="R5" t="n">
-        <v>6812136</v>
+        <v>6811930</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1061,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1075,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130307876</v>
+        <v>130307825</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,34 +1090,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444651</v>
+        <v>444646</v>
       </c>
       <c r="R6" t="n">
-        <v>6812124</v>
+        <v>6812173</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130307850</v>
+        <v>130307814</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,34 +1195,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444442</v>
+        <v>444450</v>
       </c>
       <c r="R7" t="n">
-        <v>6811950</v>
+        <v>6812087</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130307814</v>
+        <v>130307850</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,42 +1300,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444450</v>
+        <v>444442</v>
       </c>
       <c r="R8" t="n">
-        <v>6812087</v>
+        <v>6811950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,53 +1386,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130307795</v>
+        <v>130307876</v>
       </c>
       <c r="B9" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444500</v>
+        <v>444651</v>
       </c>
       <c r="R9" t="n">
-        <v>6812038</v>
+        <v>6812124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,42 +1483,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130307845</v>
+        <v>130307867</v>
       </c>
       <c r="B10" t="n">
-        <v>98991</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1522,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444430</v>
+        <v>444623</v>
       </c>
       <c r="R10" t="n">
-        <v>6812024</v>
+        <v>6812136</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130307839</v>
+        <v>130307795</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,7 +1617,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1628,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444522</v>
+        <v>444500</v>
       </c>
       <c r="R11" t="n">
-        <v>6811930</v>
+        <v>6812038</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,42 +1689,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130307825</v>
+        <v>130307845</v>
       </c>
       <c r="B12" t="n">
-        <v>57851</v>
+        <v>98991</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1733,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444646</v>
+        <v>444430</v>
       </c>
       <c r="R12" t="n">
-        <v>6812173</v>
+        <v>6812024</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,6 +1776,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130307870</v>
+        <v>130307813</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,34 +2740,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444659</v>
+        <v>444443</v>
       </c>
       <c r="R22" t="n">
-        <v>6812190</v>
+        <v>6812077</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2834,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130307869</v>
+        <v>130307822</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,34 +2845,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444632</v>
+        <v>444627</v>
       </c>
       <c r="R23" t="n">
-        <v>6812157</v>
+        <v>6812121</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3028,7 +3044,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130307813</v>
+        <v>130307838</v>
       </c>
       <c r="B25" t="n">
         <v>57851</v>
@@ -3071,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444443</v>
+        <v>444516</v>
       </c>
       <c r="R25" t="n">
-        <v>6812077</v>
+        <v>6811940</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3149,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130307822</v>
+        <v>130307869</v>
       </c>
       <c r="B26" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,42 +3160,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444627</v>
+        <v>444632</v>
       </c>
       <c r="R26" t="n">
-        <v>6812121</v>
+        <v>6812157</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,10 +3246,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130307838</v>
+        <v>130307870</v>
       </c>
       <c r="B27" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,42 +3257,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444516</v>
+        <v>444659</v>
       </c>
       <c r="R27" t="n">
-        <v>6811940</v>
+        <v>6812190</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130307874</v>
+        <v>130307827</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,34 +3451,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444695</v>
+        <v>444700</v>
       </c>
       <c r="R29" t="n">
-        <v>6812170</v>
+        <v>6812211</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3537,10 +3545,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130307862</v>
+        <v>130307807</v>
       </c>
       <c r="B30" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3548,34 +3556,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444502</v>
+        <v>444566</v>
       </c>
       <c r="R30" t="n">
-        <v>6812091</v>
+        <v>6812030</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3634,7 +3650,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130307827</v>
+        <v>130307804</v>
       </c>
       <c r="B31" t="n">
         <v>57851</v>
@@ -3677,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444700</v>
+        <v>444506</v>
       </c>
       <c r="R31" t="n">
-        <v>6812211</v>
+        <v>6812034</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3739,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130307807</v>
+        <v>130307862</v>
       </c>
       <c r="B32" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3750,42 +3766,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444566</v>
+        <v>444502</v>
       </c>
       <c r="R32" t="n">
-        <v>6812030</v>
+        <v>6812091</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,10 +3852,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130307804</v>
+        <v>130307874</v>
       </c>
       <c r="B33" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3855,42 +3863,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444506</v>
+        <v>444695</v>
       </c>
       <c r="R33" t="n">
-        <v>6812034</v>
+        <v>6812170</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130307863</v>
+        <v>130307803</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4267,34 +4267,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444505</v>
+        <v>444437</v>
       </c>
       <c r="R37" t="n">
-        <v>6812061</v>
+        <v>6812004</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4353,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130307852</v>
+        <v>130307812</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4364,34 +4372,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444645</v>
+        <v>444430</v>
       </c>
       <c r="R38" t="n">
-        <v>6812074</v>
+        <v>6812075</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,10 +4466,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130307871</v>
+        <v>130307828</v>
       </c>
       <c r="B39" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4461,34 +4477,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444705</v>
+        <v>444715</v>
       </c>
       <c r="R39" t="n">
-        <v>6812214</v>
+        <v>6812217</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4547,7 +4571,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130307803</v>
+        <v>130307800</v>
       </c>
       <c r="B40" t="n">
         <v>57851</v>
@@ -4590,10 +4614,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444437</v>
+        <v>444393</v>
       </c>
       <c r="R40" t="n">
-        <v>6812004</v>
+        <v>6812026</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,7 +4676,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130307812</v>
+        <v>130307834</v>
       </c>
       <c r="B41" t="n">
         <v>57851</v>
@@ -4695,10 +4719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444430</v>
+        <v>444688</v>
       </c>
       <c r="R41" t="n">
-        <v>6812075</v>
+        <v>6812170</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,10 +4781,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130307828</v>
+        <v>130307852</v>
       </c>
       <c r="B42" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,42 +4792,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444715</v>
+        <v>444645</v>
       </c>
       <c r="R42" t="n">
-        <v>6812217</v>
+        <v>6812074</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4862,10 +4878,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130307800</v>
+        <v>130307863</v>
       </c>
       <c r="B43" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4873,42 +4889,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444393</v>
+        <v>444505</v>
       </c>
       <c r="R43" t="n">
-        <v>6812026</v>
+        <v>6812061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4967,10 +4975,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130307834</v>
+        <v>130307871</v>
       </c>
       <c r="B44" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4978,42 +4986,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444688</v>
+        <v>444705</v>
       </c>
       <c r="R44" t="n">
-        <v>6812170</v>
+        <v>6812214</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130307877</v>
+        <v>130307809</v>
       </c>
       <c r="B45" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,34 +5083,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444661</v>
+        <v>444452</v>
       </c>
       <c r="R45" t="n">
-        <v>6812100</v>
+        <v>6812004</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5169,10 +5177,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130307851</v>
+        <v>130307820</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,34 +5188,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444648</v>
+        <v>444459</v>
       </c>
       <c r="R46" t="n">
-        <v>6812167</v>
+        <v>6812090</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5266,7 +5282,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130307809</v>
+        <v>130307831</v>
       </c>
       <c r="B47" t="n">
         <v>57851</v>
@@ -5309,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444452</v>
+        <v>444733</v>
       </c>
       <c r="R47" t="n">
-        <v>6812004</v>
+        <v>6812210</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5371,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130307820</v>
+        <v>130307851</v>
       </c>
       <c r="B48" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5382,42 +5398,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444459</v>
+        <v>444648</v>
       </c>
       <c r="R48" t="n">
-        <v>6812090</v>
+        <v>6812167</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5476,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130307831</v>
+        <v>130307877</v>
       </c>
       <c r="B49" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5487,42 +5495,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444733</v>
+        <v>444661</v>
       </c>
       <c r="R49" t="n">
-        <v>6812210</v>
+        <v>6812100</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130307866</v>
+        <v>130307861</v>
       </c>
       <c r="B50" t="n">
         <v>79211</v>
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444583</v>
+        <v>444477</v>
       </c>
       <c r="R50" t="n">
-        <v>6812106</v>
+        <v>6812077</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5678,7 +5678,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130307861</v>
+        <v>130307866</v>
       </c>
       <c r="B51" t="n">
         <v>79211</v>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444477</v>
+        <v>444583</v>
       </c>
       <c r="R51" t="n">
-        <v>6812077</v>
+        <v>6812106</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130307811</v>
+        <v>130307836</v>
       </c>
       <c r="B53" t="n">
         <v>57851</v>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444426</v>
+        <v>444552</v>
       </c>
       <c r="R53" t="n">
-        <v>6812079</v>
+        <v>6811979</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130307805</v>
+        <v>130307818</v>
       </c>
       <c r="B54" t="n">
         <v>57851</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444669</v>
+        <v>444484</v>
       </c>
       <c r="R54" t="n">
-        <v>6812147</v>
+        <v>6812056</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130307836</v>
+        <v>130307811</v>
       </c>
       <c r="B55" t="n">
         <v>57851</v>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444552</v>
+        <v>444426</v>
       </c>
       <c r="R55" t="n">
-        <v>6811979</v>
+        <v>6812079</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6195,7 +6195,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130307818</v>
+        <v>130307805</v>
       </c>
       <c r="B56" t="n">
         <v>57851</v>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444484</v>
+        <v>444669</v>
       </c>
       <c r="R56" t="n">
-        <v>6812056</v>
+        <v>6812147</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130307806</v>
+        <v>130307864</v>
       </c>
       <c r="B62" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6820,31 +6820,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6852,10 +6847,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444656</v>
+        <v>444533</v>
       </c>
       <c r="R62" t="n">
-        <v>6812108</v>
+        <v>6812085</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6896,6 +6891,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7011,10 +7007,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130307864</v>
+        <v>130307806</v>
       </c>
       <c r="B64" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7022,26 +7018,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7049,10 +7050,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444533</v>
+        <v>444656</v>
       </c>
       <c r="R64" t="n">
-        <v>6812085</v>
+        <v>6812108</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7093,7 +7094,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7629,45 +7629,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130307865</v>
+        <v>130307796</v>
       </c>
       <c r="B70" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444550</v>
+        <v>444508</v>
       </c>
       <c r="R70" t="n">
-        <v>6812103</v>
+        <v>6811946</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7700,6 +7708,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7726,53 +7739,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130307796</v>
+        <v>130307865</v>
       </c>
       <c r="B71" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444508</v>
+        <v>444550</v>
       </c>
       <c r="R71" t="n">
-        <v>6811946</v>
+        <v>6812103</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7805,11 +7810,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7941,10 +7941,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130307868</v>
+        <v>130307790</v>
       </c>
       <c r="B73" t="n">
-        <v>79211</v>
+        <v>79830</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7952,21 +7952,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7976,10 +7976,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444623</v>
+        <v>444667</v>
       </c>
       <c r="R73" t="n">
-        <v>6812168</v>
+        <v>6812191</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8139,10 +8139,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130307790</v>
+        <v>130307868</v>
       </c>
       <c r="B75" t="n">
-        <v>79830</v>
+        <v>79211</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8150,21 +8150,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8174,10 +8174,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444667</v>
+        <v>444623</v>
       </c>
       <c r="R75" t="n">
-        <v>6812191</v>
+        <v>6812168</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -1289,45 +1289,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130307850</v>
+        <v>130307845</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>98991</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444442</v>
+        <v>444430</v>
       </c>
       <c r="R8" t="n">
-        <v>6811950</v>
+        <v>6812024</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1376,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1386,7 +1395,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130307876</v>
+        <v>130307867</v>
       </c>
       <c r="B9" t="n">
         <v>79211</v>
@@ -1415,16 +1424,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444651</v>
+        <v>444623</v>
       </c>
       <c r="R9" t="n">
-        <v>6812124</v>
+        <v>6812136</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,6 +1477,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1483,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130307867</v>
+        <v>130307876</v>
       </c>
       <c r="B10" t="n">
         <v>79211</v>
@@ -1512,19 +1525,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444623</v>
+        <v>444651</v>
       </c>
       <c r="R10" t="n">
-        <v>6812136</v>
+        <v>6812124</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,7 +1575,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1584,53 +1593,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130307795</v>
+        <v>130307850</v>
       </c>
       <c r="B11" t="n">
-        <v>57044</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444500</v>
+        <v>444442</v>
       </c>
       <c r="R11" t="n">
-        <v>6812038</v>
+        <v>6811950</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130307845</v>
+        <v>130307795</v>
       </c>
       <c r="B12" t="n">
-        <v>98991</v>
+        <v>57044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,31 +1701,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1732,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444430</v>
+        <v>444500</v>
       </c>
       <c r="R12" t="n">
-        <v>6812024</v>
+        <v>6812038</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,7 +1777,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130307789</v>
+        <v>130307829</v>
       </c>
       <c r="B14" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,34 +1911,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444433</v>
+        <v>444739</v>
       </c>
       <c r="R14" t="n">
-        <v>6811944</v>
+        <v>6812234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130307829</v>
+        <v>130307846</v>
       </c>
       <c r="B15" t="n">
-        <v>57851</v>
+        <v>78969</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,42 +2016,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444739</v>
+        <v>444569</v>
       </c>
       <c r="R15" t="n">
-        <v>6812234</v>
+        <v>6812062</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130307846</v>
+        <v>130307789</v>
       </c>
       <c r="B16" t="n">
-        <v>78969</v>
+        <v>79830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,21 +2113,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444569</v>
+        <v>444433</v>
       </c>
       <c r="R16" t="n">
-        <v>6812062</v>
+        <v>6811944</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130307813</v>
+        <v>130307870</v>
       </c>
       <c r="B22" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,42 +2740,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444443</v>
+        <v>444659</v>
       </c>
       <c r="R22" t="n">
-        <v>6812077</v>
+        <v>6812190</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2834,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130307822</v>
+        <v>130307869</v>
       </c>
       <c r="B23" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2845,42 +2837,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444627</v>
+        <v>444632</v>
       </c>
       <c r="R23" t="n">
-        <v>6812121</v>
+        <v>6812157</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,7 +2923,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130307819</v>
+        <v>130307813</v>
       </c>
       <c r="B24" t="n">
         <v>57851</v>
@@ -2982,10 +2966,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444481</v>
+        <v>444443</v>
       </c>
       <c r="R24" t="n">
-        <v>6812067</v>
+        <v>6812077</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3044,7 +3028,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130307838</v>
+        <v>130307822</v>
       </c>
       <c r="B25" t="n">
         <v>57851</v>
@@ -3087,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444516</v>
+        <v>444627</v>
       </c>
       <c r="R25" t="n">
-        <v>6811940</v>
+        <v>6812121</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3149,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130307869</v>
+        <v>130307819</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3160,34 +3144,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444632</v>
+        <v>444481</v>
       </c>
       <c r="R26" t="n">
-        <v>6812157</v>
+        <v>6812067</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3246,10 +3238,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130307870</v>
+        <v>130307838</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3257,34 +3249,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444659</v>
+        <v>444516</v>
       </c>
       <c r="R27" t="n">
-        <v>6812190</v>
+        <v>6811940</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130307862</v>
+        <v>130307874</v>
       </c>
       <c r="B32" t="n">
         <v>79211</v>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444502</v>
+        <v>444695</v>
       </c>
       <c r="R32" t="n">
-        <v>6812091</v>
+        <v>6812170</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3852,7 +3852,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130307874</v>
+        <v>130307862</v>
       </c>
       <c r="B33" t="n">
         <v>79211</v>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444695</v>
+        <v>444502</v>
       </c>
       <c r="R33" t="n">
-        <v>6812170</v>
+        <v>6812091</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130307826</v>
+        <v>130307791</v>
       </c>
       <c r="B35" t="n">
-        <v>57851</v>
+        <v>79830</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4065,42 +4065,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444689</v>
+        <v>444608</v>
       </c>
       <c r="R35" t="n">
-        <v>6812204</v>
+        <v>6812061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4159,10 +4151,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130307791</v>
+        <v>130307826</v>
       </c>
       <c r="B36" t="n">
-        <v>79830</v>
+        <v>57851</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4170,34 +4162,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444608</v>
+        <v>444689</v>
       </c>
       <c r="R36" t="n">
-        <v>6812061</v>
+        <v>6812204</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130307803</v>
+        <v>130307863</v>
       </c>
       <c r="B37" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4267,42 +4267,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444437</v>
+        <v>444505</v>
       </c>
       <c r="R37" t="n">
-        <v>6812004</v>
+        <v>6812061</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,10 +4353,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130307812</v>
+        <v>130307852</v>
       </c>
       <c r="B38" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,42 +4364,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444430</v>
+        <v>444645</v>
       </c>
       <c r="R38" t="n">
-        <v>6812075</v>
+        <v>6812074</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4466,10 +4450,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130307828</v>
+        <v>130307871</v>
       </c>
       <c r="B39" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4477,42 +4461,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444715</v>
+        <v>444705</v>
       </c>
       <c r="R39" t="n">
-        <v>6812217</v>
+        <v>6812214</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,7 +4547,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130307800</v>
+        <v>130307803</v>
       </c>
       <c r="B40" t="n">
         <v>57851</v>
@@ -4614,10 +4590,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444393</v>
+        <v>444437</v>
       </c>
       <c r="R40" t="n">
-        <v>6812026</v>
+        <v>6812004</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4676,7 +4652,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130307834</v>
+        <v>130307812</v>
       </c>
       <c r="B41" t="n">
         <v>57851</v>
@@ -4719,10 +4695,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444688</v>
+        <v>444430</v>
       </c>
       <c r="R41" t="n">
-        <v>6812170</v>
+        <v>6812075</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4781,10 +4757,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130307852</v>
+        <v>130307828</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4792,34 +4768,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444645</v>
+        <v>444715</v>
       </c>
       <c r="R42" t="n">
-        <v>6812074</v>
+        <v>6812217</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4878,10 +4862,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130307863</v>
+        <v>130307800</v>
       </c>
       <c r="B43" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4889,34 +4873,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444505</v>
+        <v>444393</v>
       </c>
       <c r="R43" t="n">
-        <v>6812061</v>
+        <v>6812026</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4975,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130307871</v>
+        <v>130307834</v>
       </c>
       <c r="B44" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4986,34 +4978,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444705</v>
+        <v>444688</v>
       </c>
       <c r="R44" t="n">
-        <v>6812214</v>
+        <v>6812170</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130307809</v>
+        <v>130307877</v>
       </c>
       <c r="B45" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,42 +5083,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444452</v>
+        <v>444661</v>
       </c>
       <c r="R45" t="n">
-        <v>6812004</v>
+        <v>6812100</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5177,10 +5169,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130307820</v>
+        <v>130307851</v>
       </c>
       <c r="B46" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5188,42 +5180,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444459</v>
+        <v>444648</v>
       </c>
       <c r="R46" t="n">
-        <v>6812090</v>
+        <v>6812167</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5282,7 +5266,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130307831</v>
+        <v>130307809</v>
       </c>
       <c r="B47" t="n">
         <v>57851</v>
@@ -5325,10 +5309,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444733</v>
+        <v>444452</v>
       </c>
       <c r="R47" t="n">
-        <v>6812210</v>
+        <v>6812004</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5387,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130307851</v>
+        <v>130307820</v>
       </c>
       <c r="B48" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5398,34 +5382,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444648</v>
+        <v>444459</v>
       </c>
       <c r="R48" t="n">
-        <v>6812167</v>
+        <v>6812090</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5484,10 +5476,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130307877</v>
+        <v>130307831</v>
       </c>
       <c r="B49" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5495,34 +5487,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444661</v>
+        <v>444733</v>
       </c>
       <c r="R49" t="n">
-        <v>6812100</v>
+        <v>6812210</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5581,7 +5581,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130307861</v>
+        <v>130307866</v>
       </c>
       <c r="B50" t="n">
         <v>79211</v>
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444477</v>
+        <v>444583</v>
       </c>
       <c r="R50" t="n">
-        <v>6812077</v>
+        <v>6812106</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5678,7 +5678,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130307866</v>
+        <v>130307861</v>
       </c>
       <c r="B51" t="n">
         <v>79211</v>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444583</v>
+        <v>444477</v>
       </c>
       <c r="R51" t="n">
-        <v>6812106</v>
+        <v>6812077</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130307837</v>
+        <v>130307836</v>
       </c>
       <c r="B52" t="n">
         <v>57851</v>
@@ -5808,7 +5808,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5818,10 +5818,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444516</v>
+        <v>444552</v>
       </c>
       <c r="R52" t="n">
-        <v>6811948</v>
+        <v>6811979</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130307836</v>
+        <v>130307805</v>
       </c>
       <c r="B53" t="n">
         <v>57851</v>
@@ -5913,7 +5913,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444552</v>
+        <v>444669</v>
       </c>
       <c r="R53" t="n">
-        <v>6811979</v>
+        <v>6812147</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6195,7 +6195,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130307805</v>
+        <v>130307837</v>
       </c>
       <c r="B56" t="n">
         <v>57851</v>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444669</v>
+        <v>444516</v>
       </c>
       <c r="R56" t="n">
-        <v>6812147</v>
+        <v>6811948</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6599,10 +6599,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130307801</v>
+        <v>130307793</v>
       </c>
       <c r="B60" t="n">
-        <v>57851</v>
+        <v>57854</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6610,16 +6610,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6632,7 +6632,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6642,10 +6642,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444376</v>
+        <v>444496</v>
       </c>
       <c r="R60" t="n">
-        <v>6812020</v>
+        <v>6812068</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130307793</v>
+        <v>130307801</v>
       </c>
       <c r="B61" t="n">
-        <v>57854</v>
+        <v>57851</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6715,16 +6715,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6737,7 +6737,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444496</v>
+        <v>444376</v>
       </c>
       <c r="R61" t="n">
-        <v>6812068</v>
+        <v>6812020</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130307864</v>
+        <v>130307806</v>
       </c>
       <c r="B62" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6820,26 +6820,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6847,10 +6852,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444533</v>
+        <v>444656</v>
       </c>
       <c r="R62" t="n">
-        <v>6812085</v>
+        <v>6812108</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6891,7 +6896,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7007,10 +7011,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130307806</v>
+        <v>130307864</v>
       </c>
       <c r="B64" t="n">
-        <v>57851</v>
+        <v>79211</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7018,31 +7022,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7050,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444656</v>
+        <v>444533</v>
       </c>
       <c r="R64" t="n">
-        <v>6812108</v>
+        <v>6812085</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7094,6 +7093,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7629,53 +7629,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130307796</v>
+        <v>130307865</v>
       </c>
       <c r="B70" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444508</v>
+        <v>444550</v>
       </c>
       <c r="R70" t="n">
-        <v>6811946</v>
+        <v>6812103</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7708,11 +7700,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7739,45 +7726,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130307865</v>
+        <v>130307796</v>
       </c>
       <c r="B71" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444550</v>
+        <v>444508</v>
       </c>
       <c r="R71" t="n">
-        <v>6812103</v>
+        <v>6811946</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7810,6 +7805,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8038,48 +8038,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130307787</v>
+        <v>130307868</v>
       </c>
       <c r="B74" t="n">
-        <v>91725</v>
+        <v>79211</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444683</v>
+        <v>444623</v>
       </c>
       <c r="R74" t="n">
-        <v>6812180</v>
+        <v>6812168</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8120,7 +8117,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8139,45 +8135,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130307868</v>
+        <v>130307787</v>
       </c>
       <c r="B75" t="n">
-        <v>79211</v>
+        <v>91725</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444623</v>
+        <v>444683</v>
       </c>
       <c r="R75" t="n">
-        <v>6812168</v>
+        <v>6812180</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8218,6 +8217,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130307858</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130307860</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130307802</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130307839</v>
+        <v>130307867</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,31 +985,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1017,10 +1012,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444522</v>
+        <v>444623</v>
       </c>
       <c r="R5" t="n">
-        <v>6811930</v>
+        <v>6812136</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,6 +1056,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1079,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130307825</v>
+        <v>130307876</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,42 +1086,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444646</v>
+        <v>444651</v>
       </c>
       <c r="R6" t="n">
-        <v>6812173</v>
+        <v>6812124</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130307814</v>
+        <v>130307850</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>78976</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,42 +1183,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444450</v>
+        <v>444442</v>
       </c>
       <c r="R7" t="n">
-        <v>6812087</v>
+        <v>6811950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130307845</v>
+        <v>130307795</v>
       </c>
       <c r="B8" t="n">
-        <v>98991</v>
+        <v>57052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,31 +1280,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1332,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444430</v>
+        <v>444500</v>
       </c>
       <c r="R8" t="n">
-        <v>6812024</v>
+        <v>6812038</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1376,7 +1356,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1395,37 +1374,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130307867</v>
+        <v>130307845</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>99004</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1433,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444623</v>
+        <v>444430</v>
       </c>
       <c r="R9" t="n">
-        <v>6812136</v>
+        <v>6812024</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130307876</v>
+        <v>130307839</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,34 +1491,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444651</v>
+        <v>444522</v>
       </c>
       <c r="R10" t="n">
-        <v>6812124</v>
+        <v>6811930</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1585,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130307850</v>
+        <v>130307825</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>57859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,34 +1596,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444442</v>
+        <v>444646</v>
       </c>
       <c r="R11" t="n">
-        <v>6811950</v>
+        <v>6812173</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,32 +1690,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130307795</v>
+        <v>130307814</v>
       </c>
       <c r="B12" t="n">
-        <v>57044</v>
+        <v>57859</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1723,7 +1723,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444500</v>
+        <v>444450</v>
       </c>
       <c r="R12" t="n">
-        <v>6812038</v>
+        <v>6812087</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,7 +1798,7 @@
         <v>130307840</v>
       </c>
       <c r="B13" t="n">
-        <v>57695</v>
+        <v>57703</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130307829</v>
+        <v>130307789</v>
       </c>
       <c r="B14" t="n">
-        <v>57851</v>
+        <v>79838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,42 +1911,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444739</v>
+        <v>444433</v>
       </c>
       <c r="R14" t="n">
-        <v>6812234</v>
+        <v>6811944</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130307846</v>
+        <v>130307829</v>
       </c>
       <c r="B15" t="n">
-        <v>78969</v>
+        <v>57859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,34 +2008,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444569</v>
+        <v>444739</v>
       </c>
       <c r="R15" t="n">
-        <v>6812062</v>
+        <v>6812234</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130307789</v>
+        <v>130307846</v>
       </c>
       <c r="B16" t="n">
-        <v>79830</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,21 +2113,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444433</v>
+        <v>444569</v>
       </c>
       <c r="R16" t="n">
-        <v>6811944</v>
+        <v>6812062</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
         <v>130307817</v>
       </c>
       <c r="B17" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>130307824</v>
       </c>
       <c r="B18" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>130307808</v>
       </c>
       <c r="B19" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>130307810</v>
       </c>
       <c r="B20" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>130307843</v>
       </c>
       <c r="B21" t="n">
-        <v>57047</v>
+        <v>57055</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>130307870</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>130307869</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>130307813</v>
       </c>
       <c r="B24" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>130307822</v>
       </c>
       <c r="B25" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>130307819</v>
       </c>
       <c r="B26" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>130307838</v>
       </c>
       <c r="B27" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>130307847</v>
       </c>
       <c r="B28" t="n">
-        <v>78969</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130307827</v>
+        <v>130307874</v>
       </c>
       <c r="B29" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,42 +3451,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444700</v>
+        <v>444695</v>
       </c>
       <c r="R29" t="n">
-        <v>6812211</v>
+        <v>6812170</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,10 +3537,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130307807</v>
+        <v>130307862</v>
       </c>
       <c r="B30" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3556,42 +3548,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444566</v>
+        <v>444502</v>
       </c>
       <c r="R30" t="n">
-        <v>6812030</v>
+        <v>6812091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3650,10 +3634,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130307804</v>
+        <v>130307827</v>
       </c>
       <c r="B31" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3693,10 +3677,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444506</v>
+        <v>444700</v>
       </c>
       <c r="R31" t="n">
-        <v>6812034</v>
+        <v>6812211</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,10 +3739,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130307874</v>
+        <v>130307807</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3766,34 +3750,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444695</v>
+        <v>444566</v>
       </c>
       <c r="R32" t="n">
-        <v>6812170</v>
+        <v>6812030</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3852,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130307862</v>
+        <v>130307804</v>
       </c>
       <c r="B33" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3863,34 +3855,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444502</v>
+        <v>444506</v>
       </c>
       <c r="R33" t="n">
-        <v>6812091</v>
+        <v>6812034</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,7 +3952,7 @@
         <v>130307797</v>
       </c>
       <c r="B34" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>130307791</v>
       </c>
       <c r="B35" t="n">
-        <v>79830</v>
+        <v>79838</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>130307826</v>
       </c>
       <c r="B36" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130307863</v>
+        <v>130307812</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4267,34 +4267,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444505</v>
+        <v>444430</v>
       </c>
       <c r="R37" t="n">
-        <v>6812061</v>
+        <v>6812075</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4353,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130307852</v>
+        <v>130307828</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>57859</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4364,34 +4372,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444645</v>
+        <v>444715</v>
       </c>
       <c r="R38" t="n">
-        <v>6812074</v>
+        <v>6812217</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,10 +4466,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130307871</v>
+        <v>130307800</v>
       </c>
       <c r="B39" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4461,34 +4477,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444705</v>
+        <v>444393</v>
       </c>
       <c r="R39" t="n">
-        <v>6812214</v>
+        <v>6812026</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4547,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130307803</v>
+        <v>130307834</v>
       </c>
       <c r="B40" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4590,10 +4614,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444437</v>
+        <v>444688</v>
       </c>
       <c r="R40" t="n">
-        <v>6812004</v>
+        <v>6812170</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,10 +4676,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130307812</v>
+        <v>130307863</v>
       </c>
       <c r="B41" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4663,42 +4687,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444430</v>
+        <v>444505</v>
       </c>
       <c r="R41" t="n">
-        <v>6812075</v>
+        <v>6812061</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,10 +4773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130307828</v>
+        <v>130307852</v>
       </c>
       <c r="B42" t="n">
-        <v>57851</v>
+        <v>78976</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,42 +4784,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444715</v>
+        <v>444645</v>
       </c>
       <c r="R42" t="n">
-        <v>6812217</v>
+        <v>6812074</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4862,10 +4870,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130307800</v>
+        <v>130307871</v>
       </c>
       <c r="B43" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4873,42 +4881,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444393</v>
+        <v>444705</v>
       </c>
       <c r="R43" t="n">
-        <v>6812026</v>
+        <v>6812214</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4967,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130307834</v>
+        <v>130307803</v>
       </c>
       <c r="B44" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444688</v>
+        <v>444437</v>
       </c>
       <c r="R44" t="n">
-        <v>6812170</v>
+        <v>6812004</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5075,7 +5075,7 @@
         <v>130307877</v>
       </c>
       <c r="B45" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>130307851</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>130307809</v>
       </c>
       <c r="B47" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>130307820</v>
       </c>
       <c r="B48" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>130307831</v>
       </c>
       <c r="B49" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5581,10 +5581,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130307866</v>
+        <v>130307837</v>
       </c>
       <c r="B50" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5592,34 +5592,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444583</v>
+        <v>444516</v>
       </c>
       <c r="R50" t="n">
-        <v>6812106</v>
+        <v>6811948</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5678,10 +5686,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130307861</v>
+        <v>130307836</v>
       </c>
       <c r="B51" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5689,34 +5697,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444477</v>
+        <v>444552</v>
       </c>
       <c r="R51" t="n">
-        <v>6812077</v>
+        <v>6811979</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5791,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130307836</v>
+        <v>130307818</v>
       </c>
       <c r="B52" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5808,7 +5824,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5818,10 +5834,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444552</v>
+        <v>444484</v>
       </c>
       <c r="R52" t="n">
-        <v>6811979</v>
+        <v>6812056</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5880,10 +5896,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130307805</v>
+        <v>130307811</v>
       </c>
       <c r="B53" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5913,7 +5929,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5923,10 +5939,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444669</v>
+        <v>444426</v>
       </c>
       <c r="R53" t="n">
-        <v>6812147</v>
+        <v>6812079</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5985,10 +6001,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130307818</v>
+        <v>130307805</v>
       </c>
       <c r="B54" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6028,10 +6044,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444484</v>
+        <v>444669</v>
       </c>
       <c r="R54" t="n">
-        <v>6812056</v>
+        <v>6812147</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,10 +6106,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130307811</v>
+        <v>130307866</v>
       </c>
       <c r="B55" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6101,42 +6117,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444426</v>
+        <v>444583</v>
       </c>
       <c r="R55" t="n">
-        <v>6812079</v>
+        <v>6812106</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6195,10 +6203,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130307837</v>
+        <v>130307861</v>
       </c>
       <c r="B56" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6206,42 +6214,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444516</v>
+        <v>444477</v>
       </c>
       <c r="R56" t="n">
-        <v>6811948</v>
+        <v>6812077</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6303,7 +6303,7 @@
         <v>130307823</v>
       </c>
       <c r="B57" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>130307873</v>
       </c>
       <c r="B58" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>130307878</v>
       </c>
       <c r="B59" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6599,10 +6599,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130307793</v>
+        <v>130307801</v>
       </c>
       <c r="B60" t="n">
-        <v>57854</v>
+        <v>57859</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6610,16 +6610,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6632,7 +6632,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6642,10 +6642,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444496</v>
+        <v>444376</v>
       </c>
       <c r="R60" t="n">
-        <v>6812068</v>
+        <v>6812020</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130307801</v>
+        <v>130307793</v>
       </c>
       <c r="B61" t="n">
-        <v>57851</v>
+        <v>57862</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6715,16 +6715,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6737,7 +6737,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444376</v>
+        <v>444496</v>
       </c>
       <c r="R61" t="n">
-        <v>6812020</v>
+        <v>6812068</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130307806</v>
+        <v>130307875</v>
       </c>
       <c r="B62" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6820,42 +6820,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444656</v>
+        <v>444676</v>
       </c>
       <c r="R62" t="n">
-        <v>6812108</v>
+        <v>6812126</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6914,10 +6906,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130307875</v>
+        <v>130307864</v>
       </c>
       <c r="B63" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6943,16 +6935,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444676</v>
+        <v>444533</v>
       </c>
       <c r="R63" t="n">
-        <v>6812126</v>
+        <v>6812085</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6993,6 +6988,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7011,10 +7007,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130307864</v>
+        <v>130307806</v>
       </c>
       <c r="B64" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7022,26 +7018,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7049,10 +7050,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444533</v>
+        <v>444656</v>
       </c>
       <c r="R64" t="n">
-        <v>6812085</v>
+        <v>6812108</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7093,7 +7094,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>130307833</v>
       </c>
       <c r="B65" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>130307835</v>
       </c>
       <c r="B66" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>130307815</v>
       </c>
       <c r="B67" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>130307859</v>
       </c>
       <c r="B68" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>130307832</v>
       </c>
       <c r="B69" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7629,45 +7629,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130307865</v>
+        <v>130307796</v>
       </c>
       <c r="B70" t="n">
-        <v>79211</v>
+        <v>57052</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444550</v>
+        <v>444508</v>
       </c>
       <c r="R70" t="n">
-        <v>6812103</v>
+        <v>6811946</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7700,6 +7708,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7726,53 +7739,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130307796</v>
+        <v>130307865</v>
       </c>
       <c r="B71" t="n">
-        <v>57044</v>
+        <v>79219</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444508</v>
+        <v>444550</v>
       </c>
       <c r="R71" t="n">
-        <v>6811946</v>
+        <v>6812103</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7805,11 +7810,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7839,7 +7839,7 @@
         <v>130307821</v>
       </c>
       <c r="B72" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>130307790</v>
       </c>
       <c r="B73" t="n">
-        <v>79830</v>
+        <v>79838</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>130307868</v>
       </c>
       <c r="B74" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>130307787</v>
       </c>
       <c r="B75" t="n">
-        <v>91725</v>
+        <v>91737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130307858</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130307860</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130307802</v>
       </c>
       <c r="B4" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>130307867</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>130307876</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>130307850</v>
       </c>
       <c r="B7" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,32 +1269,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130307795</v>
+        <v>130307839</v>
       </c>
       <c r="B8" t="n">
-        <v>57052</v>
+        <v>57860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,7 +1302,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444500</v>
+        <v>444522</v>
       </c>
       <c r="R8" t="n">
-        <v>6812038</v>
+        <v>6811930</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,42 +1374,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130307845</v>
+        <v>130307825</v>
       </c>
       <c r="B9" t="n">
-        <v>99004</v>
+        <v>57860</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444430</v>
+        <v>444646</v>
       </c>
       <c r="R9" t="n">
-        <v>6812024</v>
+        <v>6812173</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,7 +1461,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130307839</v>
+        <v>130307814</v>
       </c>
       <c r="B10" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1513,7 +1512,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1523,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444522</v>
+        <v>444450</v>
       </c>
       <c r="R10" t="n">
-        <v>6811930</v>
+        <v>6812087</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130307825</v>
+        <v>130307795</v>
       </c>
       <c r="B11" t="n">
-        <v>57859</v>
+        <v>57053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,7 +1617,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1628,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444646</v>
+        <v>444500</v>
       </c>
       <c r="R11" t="n">
-        <v>6812173</v>
+        <v>6812038</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,42 +1689,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130307814</v>
+        <v>130307845</v>
       </c>
       <c r="B12" t="n">
-        <v>57859</v>
+        <v>99005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1733,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444450</v>
+        <v>444430</v>
       </c>
       <c r="R12" t="n">
-        <v>6812087</v>
+        <v>6812024</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,6 +1776,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>130307840</v>
       </c>
       <c r="B13" t="n">
-        <v>57703</v>
+        <v>57704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130307789</v>
+        <v>130307829</v>
       </c>
       <c r="B14" t="n">
-        <v>79838</v>
+        <v>57860</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,34 +1911,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444433</v>
+        <v>444739</v>
       </c>
       <c r="R14" t="n">
-        <v>6811944</v>
+        <v>6812234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130307829</v>
+        <v>130307846</v>
       </c>
       <c r="B15" t="n">
-        <v>57859</v>
+        <v>78978</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,42 +2016,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444739</v>
+        <v>444569</v>
       </c>
       <c r="R15" t="n">
-        <v>6812234</v>
+        <v>6812062</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130307846</v>
+        <v>130307789</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>79839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,21 +2113,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444569</v>
+        <v>444433</v>
       </c>
       <c r="R16" t="n">
-        <v>6812062</v>
+        <v>6811944</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
         <v>130307817</v>
       </c>
       <c r="B17" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>130307824</v>
       </c>
       <c r="B18" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>130307808</v>
       </c>
       <c r="B19" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>130307810</v>
       </c>
       <c r="B20" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>130307843</v>
       </c>
       <c r="B21" t="n">
-        <v>57055</v>
+        <v>57056</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>130307870</v>
       </c>
       <c r="B22" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>130307869</v>
       </c>
       <c r="B23" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>130307813</v>
       </c>
       <c r="B24" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>130307822</v>
       </c>
       <c r="B25" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>130307819</v>
       </c>
       <c r="B26" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>130307838</v>
       </c>
       <c r="B27" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>130307847</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130307874</v>
+        <v>130307797</v>
       </c>
       <c r="B29" t="n">
-        <v>79219</v>
+        <v>58022</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,34 +3451,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444695</v>
+        <v>444480</v>
       </c>
       <c r="R29" t="n">
-        <v>6812170</v>
+        <v>6812044</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3537,10 +3545,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130307862</v>
+        <v>130307874</v>
       </c>
       <c r="B30" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3572,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444502</v>
+        <v>444695</v>
       </c>
       <c r="R30" t="n">
-        <v>6812091</v>
+        <v>6812170</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3634,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130307827</v>
+        <v>130307862</v>
       </c>
       <c r="B31" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3645,42 +3653,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444700</v>
+        <v>444502</v>
       </c>
       <c r="R31" t="n">
-        <v>6812211</v>
+        <v>6812091</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3739,10 +3739,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130307807</v>
+        <v>130307827</v>
       </c>
       <c r="B32" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444566</v>
+        <v>444700</v>
       </c>
       <c r="R32" t="n">
-        <v>6812030</v>
+        <v>6812211</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130307804</v>
+        <v>130307807</v>
       </c>
       <c r="B33" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444506</v>
+        <v>444566</v>
       </c>
       <c r="R33" t="n">
-        <v>6812034</v>
+        <v>6812030</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130307797</v>
+        <v>130307804</v>
       </c>
       <c r="B34" t="n">
-        <v>58021</v>
+        <v>57860</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3982,7 +3982,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444480</v>
+        <v>444506</v>
       </c>
       <c r="R34" t="n">
-        <v>6812044</v>
+        <v>6812034</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130307791</v>
+        <v>130307826</v>
       </c>
       <c r="B35" t="n">
-        <v>79838</v>
+        <v>57860</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4065,34 +4065,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444608</v>
+        <v>444689</v>
       </c>
       <c r="R35" t="n">
-        <v>6812061</v>
+        <v>6812204</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4151,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130307826</v>
+        <v>130307791</v>
       </c>
       <c r="B36" t="n">
-        <v>57859</v>
+        <v>79839</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4162,42 +4170,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444689</v>
+        <v>444608</v>
       </c>
       <c r="R36" t="n">
-        <v>6812204</v>
+        <v>6812061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130307812</v>
+        <v>130307863</v>
       </c>
       <c r="B37" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4267,42 +4267,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444430</v>
+        <v>444505</v>
       </c>
       <c r="R37" t="n">
-        <v>6812075</v>
+        <v>6812061</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,10 +4353,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130307828</v>
+        <v>130307852</v>
       </c>
       <c r="B38" t="n">
-        <v>57859</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,42 +4364,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444715</v>
+        <v>444645</v>
       </c>
       <c r="R38" t="n">
-        <v>6812217</v>
+        <v>6812074</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4466,10 +4450,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130307800</v>
+        <v>130307871</v>
       </c>
       <c r="B39" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4477,42 +4461,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444393</v>
+        <v>444705</v>
       </c>
       <c r="R39" t="n">
-        <v>6812026</v>
+        <v>6812214</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,10 +4547,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130307834</v>
+        <v>130307803</v>
       </c>
       <c r="B40" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4614,10 +4590,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444688</v>
+        <v>444437</v>
       </c>
       <c r="R40" t="n">
-        <v>6812170</v>
+        <v>6812004</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4676,10 +4652,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130307863</v>
+        <v>130307812</v>
       </c>
       <c r="B41" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4687,34 +4663,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444505</v>
+        <v>444430</v>
       </c>
       <c r="R41" t="n">
-        <v>6812061</v>
+        <v>6812075</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4773,10 +4757,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130307852</v>
+        <v>130307828</v>
       </c>
       <c r="B42" t="n">
-        <v>78976</v>
+        <v>57860</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,34 +4768,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444645</v>
+        <v>444715</v>
       </c>
       <c r="R42" t="n">
-        <v>6812074</v>
+        <v>6812217</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,10 +4862,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130307871</v>
+        <v>130307800</v>
       </c>
       <c r="B43" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4881,34 +4873,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444705</v>
+        <v>444393</v>
       </c>
       <c r="R43" t="n">
-        <v>6812214</v>
+        <v>6812026</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4967,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130307803</v>
+        <v>130307834</v>
       </c>
       <c r="B44" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444437</v>
+        <v>444688</v>
       </c>
       <c r="R44" t="n">
-        <v>6812004</v>
+        <v>6812170</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130307877</v>
+        <v>130307809</v>
       </c>
       <c r="B45" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,34 +5083,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444661</v>
+        <v>444452</v>
       </c>
       <c r="R45" t="n">
-        <v>6812100</v>
+        <v>6812004</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5169,10 +5177,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130307851</v>
+        <v>130307820</v>
       </c>
       <c r="B46" t="n">
-        <v>78976</v>
+        <v>57860</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,34 +5188,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444648</v>
+        <v>444459</v>
       </c>
       <c r="R46" t="n">
-        <v>6812167</v>
+        <v>6812090</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5266,10 +5282,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130307809</v>
+        <v>130307831</v>
       </c>
       <c r="B47" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5309,10 +5325,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444452</v>
+        <v>444733</v>
       </c>
       <c r="R47" t="n">
-        <v>6812004</v>
+        <v>6812210</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5371,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130307820</v>
+        <v>130307877</v>
       </c>
       <c r="B48" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5382,42 +5398,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444459</v>
+        <v>444661</v>
       </c>
       <c r="R48" t="n">
-        <v>6812090</v>
+        <v>6812100</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5476,10 +5484,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130307831</v>
+        <v>130307851</v>
       </c>
       <c r="B49" t="n">
-        <v>57859</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5487,42 +5495,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444733</v>
+        <v>444648</v>
       </c>
       <c r="R49" t="n">
-        <v>6812210</v>
+        <v>6812167</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5581,10 +5581,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130307837</v>
+        <v>130307866</v>
       </c>
       <c r="B50" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5592,42 +5592,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444516</v>
+        <v>444583</v>
       </c>
       <c r="R50" t="n">
-        <v>6811948</v>
+        <v>6812106</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5686,10 +5678,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130307836</v>
+        <v>130307861</v>
       </c>
       <c r="B51" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5697,42 +5689,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444552</v>
+        <v>444477</v>
       </c>
       <c r="R51" t="n">
-        <v>6811979</v>
+        <v>6812077</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5791,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130307818</v>
+        <v>130307837</v>
       </c>
       <c r="B52" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5834,10 +5818,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444484</v>
+        <v>444516</v>
       </c>
       <c r="R52" t="n">
-        <v>6812056</v>
+        <v>6811948</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5896,10 +5880,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130307811</v>
+        <v>130307836</v>
       </c>
       <c r="B53" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5939,10 +5923,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444426</v>
+        <v>444552</v>
       </c>
       <c r="R53" t="n">
-        <v>6812079</v>
+        <v>6811979</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6001,10 +5985,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130307805</v>
+        <v>130307818</v>
       </c>
       <c r="B54" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6044,10 +6028,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444669</v>
+        <v>444484</v>
       </c>
       <c r="R54" t="n">
-        <v>6812147</v>
+        <v>6812056</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6106,10 +6090,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130307866</v>
+        <v>130307811</v>
       </c>
       <c r="B55" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6117,34 +6101,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444583</v>
+        <v>444426</v>
       </c>
       <c r="R55" t="n">
-        <v>6812106</v>
+        <v>6812079</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6203,10 +6195,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130307861</v>
+        <v>130307805</v>
       </c>
       <c r="B56" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6214,34 +6206,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444477</v>
+        <v>444669</v>
       </c>
       <c r="R56" t="n">
-        <v>6812077</v>
+        <v>6812147</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6303,7 +6303,7 @@
         <v>130307823</v>
       </c>
       <c r="B57" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>130307873</v>
       </c>
       <c r="B58" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6502,10 +6502,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130307878</v>
+        <v>130307801</v>
       </c>
       <c r="B59" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,34 +6513,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444642</v>
+        <v>444376</v>
       </c>
       <c r="R59" t="n">
-        <v>6812075</v>
+        <v>6812020</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6599,10 +6607,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130307801</v>
+        <v>130307793</v>
       </c>
       <c r="B60" t="n">
-        <v>57859</v>
+        <v>57863</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6610,16 +6618,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6632,7 +6640,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6642,10 +6650,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444376</v>
+        <v>444496</v>
       </c>
       <c r="R60" t="n">
-        <v>6812020</v>
+        <v>6812068</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6704,10 +6712,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130307793</v>
+        <v>130307878</v>
       </c>
       <c r="B61" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6715,42 +6723,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444496</v>
+        <v>444642</v>
       </c>
       <c r="R61" t="n">
-        <v>6812068</v>
+        <v>6812075</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6812,7 +6812,7 @@
         <v>130307875</v>
       </c>
       <c r="B62" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>130307864</v>
       </c>
       <c r="B63" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>130307806</v>
       </c>
       <c r="B64" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>130307833</v>
       </c>
       <c r="B65" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>130307835</v>
       </c>
       <c r="B66" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>130307815</v>
       </c>
       <c r="B67" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>130307859</v>
       </c>
       <c r="B68" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>130307832</v>
       </c>
       <c r="B69" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>130307796</v>
       </c>
       <c r="B70" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>130307865</v>
       </c>
       <c r="B71" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>130307821</v>
       </c>
       <c r="B72" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>130307790</v>
       </c>
       <c r="B73" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>130307868</v>
       </c>
       <c r="B74" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>130307787</v>
       </c>
       <c r="B75" t="n">
-        <v>91737</v>
+        <v>91738</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130307858</v>
+        <v>130307802</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444436</v>
+        <v>444397</v>
       </c>
       <c r="R2" t="n">
-        <v>6811920</v>
+        <v>6812004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130307860</v>
+        <v>130307858</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444487</v>
+        <v>444436</v>
       </c>
       <c r="R3" t="n">
-        <v>6812030</v>
+        <v>6811920</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130307802</v>
+        <v>130307860</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444397</v>
+        <v>444487</v>
       </c>
       <c r="R4" t="n">
-        <v>6812004</v>
+        <v>6812030</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
         <v>130307867</v>
       </c>
       <c r="B5" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>130307876</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>130307850</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>130307839</v>
       </c>
       <c r="B8" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>130307825</v>
       </c>
       <c r="B9" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>130307814</v>
       </c>
       <c r="B10" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>130307845</v>
       </c>
       <c r="B12" t="n">
-        <v>99005</v>
+        <v>99008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130307840</v>
       </c>
       <c r="B13" t="n">
-        <v>57704</v>
+        <v>57705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130307829</v>
+        <v>130307789</v>
       </c>
       <c r="B14" t="n">
-        <v>57860</v>
+        <v>79840</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,42 +1911,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444739</v>
+        <v>444433</v>
       </c>
       <c r="R14" t="n">
-        <v>6812234</v>
+        <v>6811944</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130307846</v>
+        <v>130307829</v>
       </c>
       <c r="B15" t="n">
-        <v>78978</v>
+        <v>57861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,34 +2008,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444569</v>
+        <v>444739</v>
       </c>
       <c r="R15" t="n">
-        <v>6812062</v>
+        <v>6812234</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130307789</v>
+        <v>130307846</v>
       </c>
       <c r="B16" t="n">
-        <v>79839</v>
+        <v>78979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,21 +2113,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444433</v>
+        <v>444569</v>
       </c>
       <c r="R16" t="n">
-        <v>6811944</v>
+        <v>6812062</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
         <v>130307817</v>
       </c>
       <c r="B17" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>130307824</v>
       </c>
       <c r="B18" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>130307808</v>
       </c>
       <c r="B19" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>130307810</v>
       </c>
       <c r="B20" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130307870</v>
+        <v>130307813</v>
       </c>
       <c r="B22" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,34 +2740,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444659</v>
+        <v>444443</v>
       </c>
       <c r="R22" t="n">
-        <v>6812190</v>
+        <v>6812077</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2834,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130307869</v>
+        <v>130307822</v>
       </c>
       <c r="B23" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2837,34 +2845,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444632</v>
+        <v>444627</v>
       </c>
       <c r="R23" t="n">
-        <v>6812157</v>
+        <v>6812121</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130307813</v>
+        <v>130307819</v>
       </c>
       <c r="B24" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2966,10 +2982,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444443</v>
+        <v>444481</v>
       </c>
       <c r="R24" t="n">
-        <v>6812077</v>
+        <v>6812067</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3028,10 +3044,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130307822</v>
+        <v>130307838</v>
       </c>
       <c r="B25" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444627</v>
+        <v>444516</v>
       </c>
       <c r="R25" t="n">
-        <v>6812121</v>
+        <v>6811940</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3149,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130307819</v>
+        <v>130307870</v>
       </c>
       <c r="B26" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,42 +3160,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444481</v>
+        <v>444659</v>
       </c>
       <c r="R26" t="n">
-        <v>6812067</v>
+        <v>6812190</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3238,10 +3246,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130307838</v>
+        <v>130307869</v>
       </c>
       <c r="B27" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,42 +3257,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444516</v>
+        <v>444632</v>
       </c>
       <c r="R27" t="n">
-        <v>6811940</v>
+        <v>6812157</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,7 +3346,7 @@
         <v>130307847</v>
       </c>
       <c r="B28" t="n">
-        <v>78978</v>
+        <v>78979</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130307797</v>
+        <v>130307874</v>
       </c>
       <c r="B29" t="n">
-        <v>58022</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,42 +3451,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444480</v>
+        <v>444695</v>
       </c>
       <c r="R29" t="n">
-        <v>6812044</v>
+        <v>6812170</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,10 +3537,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130307874</v>
+        <v>130307862</v>
       </c>
       <c r="B30" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3580,10 +3572,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444695</v>
+        <v>444502</v>
       </c>
       <c r="R30" t="n">
-        <v>6812170</v>
+        <v>6812091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3634,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130307862</v>
+        <v>130307827</v>
       </c>
       <c r="B31" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3653,34 +3645,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444502</v>
+        <v>444700</v>
       </c>
       <c r="R31" t="n">
-        <v>6812091</v>
+        <v>6812211</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3739,10 +3739,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130307827</v>
+        <v>130307807</v>
       </c>
       <c r="B32" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444700</v>
+        <v>444566</v>
       </c>
       <c r="R32" t="n">
-        <v>6812211</v>
+        <v>6812030</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130307807</v>
+        <v>130307804</v>
       </c>
       <c r="B33" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444566</v>
+        <v>444506</v>
       </c>
       <c r="R33" t="n">
-        <v>6812030</v>
+        <v>6812034</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130307804</v>
+        <v>130307797</v>
       </c>
       <c r="B34" t="n">
-        <v>57860</v>
+        <v>58023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3982,7 +3982,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444506</v>
+        <v>444480</v>
       </c>
       <c r="R34" t="n">
-        <v>6812034</v>
+        <v>6812044</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4057,7 +4057,7 @@
         <v>130307826</v>
       </c>
       <c r="B35" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>130307791</v>
       </c>
       <c r="B36" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130307863</v>
+        <v>130307803</v>
       </c>
       <c r="B37" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4267,34 +4267,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444505</v>
+        <v>444437</v>
       </c>
       <c r="R37" t="n">
-        <v>6812061</v>
+        <v>6812004</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4353,10 +4361,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130307852</v>
+        <v>130307812</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>57861</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4364,34 +4372,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444645</v>
+        <v>444430</v>
       </c>
       <c r="R38" t="n">
-        <v>6812074</v>
+        <v>6812075</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4450,10 +4466,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130307871</v>
+        <v>130307828</v>
       </c>
       <c r="B39" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4461,34 +4477,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444705</v>
+        <v>444715</v>
       </c>
       <c r="R39" t="n">
-        <v>6812214</v>
+        <v>6812217</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4547,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130307803</v>
+        <v>130307800</v>
       </c>
       <c r="B40" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4590,10 +4614,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444437</v>
+        <v>444393</v>
       </c>
       <c r="R40" t="n">
-        <v>6812004</v>
+        <v>6812026</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,10 +4676,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130307812</v>
+        <v>130307834</v>
       </c>
       <c r="B41" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4695,10 +4719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444430</v>
+        <v>444688</v>
       </c>
       <c r="R41" t="n">
-        <v>6812075</v>
+        <v>6812170</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,10 +4781,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130307828</v>
+        <v>130307863</v>
       </c>
       <c r="B42" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4768,42 +4792,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444715</v>
+        <v>444505</v>
       </c>
       <c r="R42" t="n">
-        <v>6812217</v>
+        <v>6812061</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4862,10 +4878,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130307800</v>
+        <v>130307871</v>
       </c>
       <c r="B43" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4873,42 +4889,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444393</v>
+        <v>444705</v>
       </c>
       <c r="R43" t="n">
-        <v>6812026</v>
+        <v>6812214</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4967,10 +4975,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130307834</v>
+        <v>130307852</v>
       </c>
       <c r="B44" t="n">
-        <v>57860</v>
+        <v>78978</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4978,42 +4986,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444688</v>
+        <v>444645</v>
       </c>
       <c r="R44" t="n">
-        <v>6812170</v>
+        <v>6812074</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130307809</v>
+        <v>130307877</v>
       </c>
       <c r="B45" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,42 +5083,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444452</v>
+        <v>444661</v>
       </c>
       <c r="R45" t="n">
-        <v>6812004</v>
+        <v>6812100</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5177,10 +5169,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130307820</v>
+        <v>130307851</v>
       </c>
       <c r="B46" t="n">
-        <v>57860</v>
+        <v>78978</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5188,42 +5180,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444459</v>
+        <v>444648</v>
       </c>
       <c r="R46" t="n">
-        <v>6812090</v>
+        <v>6812167</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5282,10 +5266,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130307831</v>
+        <v>130307809</v>
       </c>
       <c r="B47" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5325,10 +5309,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444733</v>
+        <v>444452</v>
       </c>
       <c r="R47" t="n">
-        <v>6812210</v>
+        <v>6812004</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5387,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130307877</v>
+        <v>130307820</v>
       </c>
       <c r="B48" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5398,34 +5382,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444661</v>
+        <v>444459</v>
       </c>
       <c r="R48" t="n">
-        <v>6812100</v>
+        <v>6812090</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5484,10 +5476,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130307851</v>
+        <v>130307831</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>57861</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5495,34 +5487,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444648</v>
+        <v>444733</v>
       </c>
       <c r="R49" t="n">
-        <v>6812167</v>
+        <v>6812210</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5584,7 +5584,7 @@
         <v>130307866</v>
       </c>
       <c r="B50" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>130307861</v>
       </c>
       <c r="B51" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>130307837</v>
       </c>
       <c r="B52" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>130307836</v>
       </c>
       <c r="B53" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>130307818</v>
       </c>
       <c r="B54" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>130307811</v>
       </c>
       <c r="B55" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>130307805</v>
       </c>
       <c r="B56" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>130307823</v>
       </c>
       <c r="B57" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130307873</v>
+        <v>130307801</v>
       </c>
       <c r="B58" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6416,34 +6416,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444714</v>
+        <v>444376</v>
       </c>
       <c r="R58" t="n">
-        <v>6812206</v>
+        <v>6812020</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6502,10 +6510,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130307801</v>
+        <v>130307793</v>
       </c>
       <c r="B59" t="n">
-        <v>57860</v>
+        <v>57864</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6513,16 +6521,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6535,7 +6543,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6545,10 +6553,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444376</v>
+        <v>444496</v>
       </c>
       <c r="R59" t="n">
-        <v>6812020</v>
+        <v>6812068</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6607,10 +6615,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130307793</v>
+        <v>130307873</v>
       </c>
       <c r="B60" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6618,42 +6626,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444496</v>
+        <v>444714</v>
       </c>
       <c r="R60" t="n">
-        <v>6812068</v>
+        <v>6812206</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6715,7 +6715,7 @@
         <v>130307878</v>
       </c>
       <c r="B61" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130307875</v>
+        <v>130307806</v>
       </c>
       <c r="B62" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6820,34 +6820,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444676</v>
+        <v>444656</v>
       </c>
       <c r="R62" t="n">
-        <v>6812126</v>
+        <v>6812108</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6906,10 +6914,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130307864</v>
+        <v>130307875</v>
       </c>
       <c r="B63" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6935,19 +6943,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444533</v>
+        <v>444676</v>
       </c>
       <c r="R63" t="n">
-        <v>6812085</v>
+        <v>6812126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6988,7 +6993,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7007,10 +7011,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130307806</v>
+        <v>130307864</v>
       </c>
       <c r="B64" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7018,31 +7022,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7050,10 +7049,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444656</v>
+        <v>444533</v>
       </c>
       <c r="R64" t="n">
-        <v>6812108</v>
+        <v>6812085</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7094,6 +7093,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7112,10 +7112,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130307833</v>
+        <v>130307859</v>
       </c>
       <c r="B65" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7123,42 +7123,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444702</v>
+        <v>444491</v>
       </c>
       <c r="R65" t="n">
-        <v>6812194</v>
+        <v>6812073</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7217,10 +7209,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130307835</v>
+        <v>130307833</v>
       </c>
       <c r="B66" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7260,10 +7252,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>444643</v>
+        <v>444702</v>
       </c>
       <c r="R66" t="n">
-        <v>6812117</v>
+        <v>6812194</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7322,10 +7314,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130307815</v>
+        <v>130307835</v>
       </c>
       <c r="B67" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7365,10 +7357,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444464</v>
+        <v>444643</v>
       </c>
       <c r="R67" t="n">
-        <v>6812074</v>
+        <v>6812117</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7427,10 +7419,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130307859</v>
+        <v>130307815</v>
       </c>
       <c r="B68" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7438,34 +7430,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444491</v>
+        <v>444464</v>
       </c>
       <c r="R68" t="n">
-        <v>6812073</v>
+        <v>6812074</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7527,7 +7527,7 @@
         <v>130307832</v>
       </c>
       <c r="B69" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7629,53 +7629,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130307796</v>
+        <v>130307865</v>
       </c>
       <c r="B70" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444508</v>
+        <v>444550</v>
       </c>
       <c r="R70" t="n">
-        <v>6811946</v>
+        <v>6812103</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7708,11 +7700,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7739,45 +7726,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130307865</v>
+        <v>130307796</v>
       </c>
       <c r="B71" t="n">
-        <v>79220</v>
+        <v>57053</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444550</v>
+        <v>444508</v>
       </c>
       <c r="R71" t="n">
-        <v>6812103</v>
+        <v>6811946</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7810,6 +7805,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7839,7 +7839,7 @@
         <v>130307821</v>
       </c>
       <c r="B72" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>130307790</v>
       </c>
       <c r="B73" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8038,45 +8038,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130307868</v>
+        <v>130307787</v>
       </c>
       <c r="B74" t="n">
-        <v>79220</v>
+        <v>91739</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444623</v>
+        <v>444683</v>
       </c>
       <c r="R74" t="n">
-        <v>6812168</v>
+        <v>6812180</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8117,6 +8120,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8135,48 +8139,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130307787</v>
+        <v>130307868</v>
       </c>
       <c r="B75" t="n">
-        <v>91738</v>
+        <v>79221</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444683</v>
+        <v>444623</v>
       </c>
       <c r="R75" t="n">
-        <v>6812180</v>
+        <v>6812168</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8217,7 +8218,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130307802</v>
+        <v>130307858</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444397</v>
+        <v>444436</v>
       </c>
       <c r="R2" t="n">
-        <v>6812004</v>
+        <v>6811920</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130307858</v>
+        <v>130307860</v>
       </c>
       <c r="B3" t="n">
         <v>79221</v>
@@ -815,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444436</v>
+        <v>444487</v>
       </c>
       <c r="R3" t="n">
-        <v>6811920</v>
+        <v>6812030</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130307860</v>
+        <v>130307802</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444487</v>
+        <v>444397</v>
       </c>
       <c r="R4" t="n">
-        <v>6812030</v>
+        <v>6812004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130307789</v>
+        <v>130307829</v>
       </c>
       <c r="B14" t="n">
-        <v>79840</v>
+        <v>57861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,34 +1911,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444433</v>
+        <v>444739</v>
       </c>
       <c r="R14" t="n">
-        <v>6811944</v>
+        <v>6812234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130307829</v>
+        <v>130307789</v>
       </c>
       <c r="B15" t="n">
-        <v>57861</v>
+        <v>79840</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2008,42 +2016,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444739</v>
+        <v>444433</v>
       </c>
       <c r="R15" t="n">
-        <v>6812234</v>
+        <v>6811944</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130307870</v>
+        <v>130307847</v>
       </c>
       <c r="B26" t="n">
-        <v>79221</v>
+        <v>78979</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3160,21 +3160,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444659</v>
+        <v>444648</v>
       </c>
       <c r="R26" t="n">
-        <v>6812190</v>
+        <v>6812167</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3246,7 +3246,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130307869</v>
+        <v>130307870</v>
       </c>
       <c r="B27" t="n">
         <v>79221</v>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444632</v>
+        <v>444659</v>
       </c>
       <c r="R27" t="n">
-        <v>6812157</v>
+        <v>6812190</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130307847</v>
+        <v>130307869</v>
       </c>
       <c r="B28" t="n">
-        <v>78979</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444648</v>
+        <v>444632</v>
       </c>
       <c r="R28" t="n">
-        <v>6812167</v>
+        <v>6812157</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130307874</v>
+        <v>130307804</v>
       </c>
       <c r="B29" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,34 +3451,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444695</v>
+        <v>444506</v>
       </c>
       <c r="R29" t="n">
-        <v>6812170</v>
+        <v>6812034</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3537,7 +3545,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130307862</v>
+        <v>130307874</v>
       </c>
       <c r="B30" t="n">
         <v>79221</v>
@@ -3572,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444502</v>
+        <v>444695</v>
       </c>
       <c r="R30" t="n">
-        <v>6812091</v>
+        <v>6812170</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3634,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130307827</v>
+        <v>130307862</v>
       </c>
       <c r="B31" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3645,42 +3653,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444700</v>
+        <v>444502</v>
       </c>
       <c r="R31" t="n">
-        <v>6812211</v>
+        <v>6812091</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3739,7 +3739,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130307807</v>
+        <v>130307827</v>
       </c>
       <c r="B32" t="n">
         <v>57861</v>
@@ -3772,7 +3772,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444566</v>
+        <v>444700</v>
       </c>
       <c r="R32" t="n">
-        <v>6812030</v>
+        <v>6812211</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130307804</v>
+        <v>130307807</v>
       </c>
       <c r="B33" t="n">
         <v>57861</v>
@@ -3877,7 +3877,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444506</v>
+        <v>444566</v>
       </c>
       <c r="R33" t="n">
-        <v>6812034</v>
+        <v>6812030</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130307826</v>
+        <v>130307791</v>
       </c>
       <c r="B35" t="n">
-        <v>57861</v>
+        <v>79840</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4065,42 +4065,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444689</v>
+        <v>444608</v>
       </c>
       <c r="R35" t="n">
-        <v>6812204</v>
+        <v>6812061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4159,10 +4151,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130307791</v>
+        <v>130307826</v>
       </c>
       <c r="B36" t="n">
-        <v>79840</v>
+        <v>57861</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4170,34 +4162,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444608</v>
+        <v>444689</v>
       </c>
       <c r="R36" t="n">
-        <v>6812061</v>
+        <v>6812204</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130307803</v>
+        <v>130307863</v>
       </c>
       <c r="B37" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4267,42 +4267,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444437</v>
+        <v>444505</v>
       </c>
       <c r="R37" t="n">
-        <v>6812004</v>
+        <v>6812061</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,10 +4353,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130307812</v>
+        <v>130307852</v>
       </c>
       <c r="B38" t="n">
-        <v>57861</v>
+        <v>78978</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,42 +4364,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444430</v>
+        <v>444645</v>
       </c>
       <c r="R38" t="n">
-        <v>6812075</v>
+        <v>6812074</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4466,10 +4450,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130307828</v>
+        <v>130307871</v>
       </c>
       <c r="B39" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4477,42 +4461,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444715</v>
+        <v>444705</v>
       </c>
       <c r="R39" t="n">
-        <v>6812217</v>
+        <v>6812214</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,7 +4547,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130307800</v>
+        <v>130307803</v>
       </c>
       <c r="B40" t="n">
         <v>57861</v>
@@ -4614,10 +4590,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444393</v>
+        <v>444437</v>
       </c>
       <c r="R40" t="n">
-        <v>6812026</v>
+        <v>6812004</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4676,7 +4652,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130307834</v>
+        <v>130307812</v>
       </c>
       <c r="B41" t="n">
         <v>57861</v>
@@ -4719,10 +4695,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444688</v>
+        <v>444430</v>
       </c>
       <c r="R41" t="n">
-        <v>6812170</v>
+        <v>6812075</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4781,10 +4757,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130307863</v>
+        <v>130307828</v>
       </c>
       <c r="B42" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4792,34 +4768,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444505</v>
+        <v>444715</v>
       </c>
       <c r="R42" t="n">
-        <v>6812061</v>
+        <v>6812217</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4878,10 +4862,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130307871</v>
+        <v>130307800</v>
       </c>
       <c r="B43" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4889,34 +4873,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444705</v>
+        <v>444393</v>
       </c>
       <c r="R43" t="n">
-        <v>6812214</v>
+        <v>6812026</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4975,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130307852</v>
+        <v>130307834</v>
       </c>
       <c r="B44" t="n">
-        <v>78978</v>
+        <v>57861</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4986,34 +4978,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444645</v>
+        <v>444688</v>
       </c>
       <c r="R44" t="n">
-        <v>6812074</v>
+        <v>6812170</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130307801</v>
+        <v>130307873</v>
       </c>
       <c r="B58" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6416,42 +6416,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444376</v>
+        <v>444714</v>
       </c>
       <c r="R58" t="n">
-        <v>6812020</v>
+        <v>6812206</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6510,10 +6502,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130307793</v>
+        <v>130307878</v>
       </c>
       <c r="B59" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6521,42 +6513,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444496</v>
+        <v>444642</v>
       </c>
       <c r="R59" t="n">
-        <v>6812068</v>
+        <v>6812075</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6615,10 +6599,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130307873</v>
+        <v>130307793</v>
       </c>
       <c r="B60" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6626,34 +6610,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444714</v>
+        <v>444496</v>
       </c>
       <c r="R60" t="n">
-        <v>6812206</v>
+        <v>6812068</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6712,10 +6704,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130307878</v>
+        <v>130307801</v>
       </c>
       <c r="B61" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6723,34 +6715,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444642</v>
+        <v>444376</v>
       </c>
       <c r="R61" t="n">
-        <v>6812075</v>
+        <v>6812020</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8038,48 +8038,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130307787</v>
+        <v>130307868</v>
       </c>
       <c r="B74" t="n">
-        <v>91739</v>
+        <v>79221</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444683</v>
+        <v>444623</v>
       </c>
       <c r="R74" t="n">
-        <v>6812180</v>
+        <v>6812168</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8120,7 +8117,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8139,45 +8135,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130307868</v>
+        <v>130307787</v>
       </c>
       <c r="B75" t="n">
-        <v>79221</v>
+        <v>91739</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gumpersberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>444623</v>
+        <v>444683</v>
       </c>
       <c r="R75" t="n">
-        <v>6812168</v>
+        <v>6812180</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8218,6 +8217,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57095-2025 artfynd.xlsx
+++ b/artfynd/A 57095-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307787</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307858</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307859</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307860</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307861</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307862</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307863</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307864</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307865</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307866</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1751,6 +1806,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307867</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307868</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1945,6 +2010,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307869</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2042,6 +2112,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307870</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2139,6 +2214,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307871</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2236,6 +2316,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307873</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2333,6 +2418,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307874</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2430,6 +2520,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307875</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2527,6 +2622,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307876</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2624,6 +2724,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307877</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2721,6 +2826,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307878</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2818,6 +2928,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307850</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2915,6 +3030,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307851</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3012,6 +3132,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307852</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3109,6 +3234,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307789</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3206,6 +3336,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307790</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3303,6 +3438,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307791</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3408,6 +3548,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307800</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3513,6 +3658,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307801</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3618,6 +3768,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307802</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3723,6 +3878,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307803</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3828,6 +3988,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307804</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3933,6 +4098,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307805</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4038,6 +4208,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307806</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4143,6 +4318,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307807</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4248,6 +4428,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307808</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4353,6 +4538,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307809</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4458,6 +4648,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307810</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4563,6 +4758,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307811</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4668,6 +4868,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307812</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4773,6 +4978,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307813</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4878,6 +5088,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307814</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4983,6 +5198,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307815</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5088,6 +5308,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307817</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5193,6 +5418,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307818</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5298,6 +5528,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307819</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5403,6 +5638,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307820</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5508,6 +5748,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307821</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5613,6 +5858,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307822</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5718,6 +5968,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307823</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5823,6 +6078,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307824</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5928,6 +6188,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307825</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6033,6 +6298,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307826</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6138,6 +6408,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307827</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6243,6 +6518,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307828</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6348,6 +6628,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307829</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6453,6 +6738,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307830</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6558,6 +6848,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307831</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6663,6 +6958,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307832</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6768,6 +7068,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307833</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6873,6 +7178,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307834</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6978,6 +7288,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307835</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7083,6 +7398,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307836</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7188,6 +7508,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307837</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7293,6 +7618,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307838</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7398,6 +7728,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307839</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7503,6 +7838,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307793</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7608,6 +7948,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307794</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7713,6 +8058,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307795</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7823,6 +8173,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307796</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7933,6 +8288,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307843</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8038,6 +8398,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307840</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8143,6 +8508,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307797</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8249,6 +8619,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307845</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8356,6 +8731,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307857</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8453,6 +8833,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307846</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8550,8 +8935,92 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130307847</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>